--- a/oPool_display/oPool_result/validated_abs_freq.xlsx
+++ b/oPool_display/oPool_result/validated_abs_freq.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/owenouyang/Desktop/Git_Repo/oPool_display/oPool_display/oPool_result/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F959E8CE-EB19-FA47-B35C-4E5DD85957CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5E46EE0-0A59-4F47-B36E-E795BB3968BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39480" yWindow="540" windowWidth="27640" windowHeight="16940" xr2:uid="{285F9910-8067-5D44-BABC-B61A2797DCFB}"/>
+    <workbookView xWindow="32360" yWindow="500" windowWidth="27640" windowHeight="16940" xr2:uid="{285F9910-8067-5D44-BABC-B61A2797DCFB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$AK$25</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -576,6 +579,7 @@
   <cols>
     <col min="1" max="1" width="19.6640625" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
+    <col min="10" max="12" width="31.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37" x14ac:dyDescent="0.2">
@@ -806,793 +810,793 @@
     </row>
     <row r="3" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="1">
-        <v>2.9010453433387002E-4</v>
-      </c>
-      <c r="C3">
-        <v>1.18313191920899E-3</v>
+        <v>58</v>
+      </c>
+      <c r="B3">
+        <v>1.35188712999584E-2</v>
+      </c>
+      <c r="C3" s="1">
+        <v>5.1762021465393004E-4</v>
       </c>
       <c r="D3" s="1">
-        <v>9.4067182781942802E-6</v>
-      </c>
-      <c r="E3" s="1">
-        <v>7.8162995900784996E-4</v>
-      </c>
-      <c r="F3" s="1">
-        <v>9.9365304119933902E-5</v>
-      </c>
-      <c r="G3" s="1">
-        <v>6.6105504384998399E-5</v>
+        <v>6.3965684291721005E-4</v>
+      </c>
+      <c r="E3">
+        <v>4.3250191065100996E-3</v>
+      </c>
+      <c r="F3">
+        <v>1.3662729316490901E-3</v>
+      </c>
+      <c r="G3">
+        <v>5.4426865276981998E-3</v>
       </c>
       <c r="H3" s="1">
-        <v>4.0052869788120301E-5</v>
+        <v>2.9038330596386998E-4</v>
       </c>
       <c r="I3" s="1">
-        <v>3.7394360930371699E-5</v>
-      </c>
-      <c r="J3" s="1">
-        <v>6.2213042342196598E-5</v>
+        <v>3.8640839628049998E-4</v>
+      </c>
+      <c r="J3">
+        <v>1.9211387475270299E-2</v>
       </c>
       <c r="K3" s="1">
-        <v>3.5061006150702002E-4</v>
-      </c>
-      <c r="L3" s="1">
-        <v>2.76706819900754E-5</v>
-      </c>
-      <c r="M3" s="1">
-        <v>1.2447874525423999E-4</v>
-      </c>
-      <c r="N3" s="1">
-        <v>1.9748990332869199E-5</v>
-      </c>
-      <c r="O3" s="1">
-        <v>3.93089486821674E-5</v>
+        <v>6.3109811071263998E-4</v>
+      </c>
+      <c r="L3">
+        <v>1.49421682746407E-3</v>
+      </c>
+      <c r="M3">
+        <v>5.5393041638140197E-3</v>
+      </c>
+      <c r="N3">
+        <v>1.09606896347424E-3</v>
+      </c>
+      <c r="O3">
+        <v>7.15422866015448E-3</v>
       </c>
       <c r="P3" s="1">
-        <v>8.74431619447359E-6</v>
+        <v>4.6344875830709999E-4</v>
       </c>
       <c r="Q3" s="1">
-        <v>1.11316428078455E-5</v>
-      </c>
-      <c r="R3" s="1">
-        <v>1.19345E-4</v>
-      </c>
-      <c r="S3" s="1">
-        <v>2.76E-5</v>
-      </c>
-      <c r="T3" s="1">
-        <v>1.4800000000000001E-5</v>
-      </c>
-      <c r="U3">
-        <v>2.6648349999999999E-3</v>
-      </c>
-      <c r="V3" s="1">
-        <v>8.5799999999999998E-5</v>
+        <v>1.6697464211768001E-4</v>
+      </c>
+      <c r="R3">
+        <v>7.2040790000000004E-3</v>
+      </c>
+      <c r="S3">
+        <v>1.2774076000000001E-2</v>
+      </c>
+      <c r="T3">
+        <v>1.3310069999999999E-3</v>
+      </c>
+      <c r="U3" s="1">
+        <v>4.9196999999999999E-4</v>
+      </c>
+      <c r="V3">
+        <v>4.5490440000000004E-3</v>
       </c>
       <c r="W3" s="1">
-        <v>3.6544799999999999E-4</v>
+        <v>8.4053100000000005E-4</v>
       </c>
       <c r="X3">
-        <v>1.8261308583889001E-4</v>
+        <v>1.12897854833338E-2</v>
       </c>
       <c r="Y3" s="1">
-        <v>7.8429299071185003E-4</v>
-      </c>
-      <c r="Z3">
-        <v>2.4822391509030199E-3</v>
-      </c>
-      <c r="AA3" s="1">
-        <v>2.0278491280247999E-4</v>
-      </c>
-      <c r="AB3" s="1">
-        <v>2.4536866642128999E-4</v>
-      </c>
-      <c r="AC3" s="1">
-        <v>9.3426510706678102E-5</v>
-      </c>
-      <c r="AD3" s="1">
-        <v>1.6111996276337999E-4</v>
-      </c>
-      <c r="AE3" s="1">
-        <v>9.4934305460621206E-6</v>
-      </c>
-      <c r="AF3" s="1">
-        <v>2.7084503651392001E-4</v>
-      </c>
-      <c r="AG3" s="1">
-        <v>2.9924504749445998E-4</v>
-      </c>
-      <c r="AH3" s="1">
-        <v>2.1807872642023701E-5</v>
-      </c>
-      <c r="AI3" s="1">
-        <v>6.92648688585149E-5</v>
-      </c>
-      <c r="AJ3" s="1">
-        <v>2.7649769585253399E-5</v>
-      </c>
-      <c r="AK3" s="1">
-        <v>7.4420266126871593E-5</v>
+        <v>6.9617018276669997E-4</v>
+      </c>
+      <c r="Z3" s="1">
+        <v>6.3339895574766002E-4</v>
+      </c>
+      <c r="AA3">
+        <v>2.1855707268712502E-3</v>
+      </c>
+      <c r="AB3">
+        <v>7.13613871508608E-3</v>
+      </c>
+      <c r="AC3">
+        <v>1.27060054561082E-3</v>
+      </c>
+      <c r="AD3">
+        <v>1.01505576540933E-2</v>
+      </c>
+      <c r="AE3">
+        <v>1.54647983595352E-2</v>
+      </c>
+      <c r="AF3">
+        <v>1.9460717438407799E-3</v>
+      </c>
+      <c r="AG3">
+        <v>1.03453287848086E-3</v>
+      </c>
+      <c r="AH3">
+        <v>4.9394831534183802E-3</v>
+      </c>
+      <c r="AI3">
+        <v>1.5169006280014699E-2</v>
+      </c>
+      <c r="AJ3">
+        <v>1.2626728110599001E-3</v>
+      </c>
+      <c r="AK3">
+        <v>1.4467299735063799E-2</v>
       </c>
     </row>
     <row r="4" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="1">
-        <v>3.0944483662279001E-4</v>
+        <v>50</v>
+      </c>
+      <c r="B4">
+        <v>1.32577772190579E-2</v>
       </c>
       <c r="C4" s="1">
-        <v>1.05636778500802E-5</v>
+        <v>3.2747401335248E-4</v>
       </c>
       <c r="D4">
-        <v>2.4833736254432901E-3</v>
-      </c>
-      <c r="E4" s="1">
-        <v>1.5632599180157001E-4</v>
-      </c>
-      <c r="F4" s="1">
-        <v>4.9682652059966897E-5</v>
-      </c>
-      <c r="G4" s="1">
-        <v>8.8140672513331204E-5</v>
+        <v>0.27852352149905402</v>
+      </c>
+      <c r="E4">
+        <v>2.7617591884944001E-3</v>
+      </c>
+      <c r="F4">
+        <v>2.35992597284843E-3</v>
+      </c>
+      <c r="G4">
+        <v>5.4647216958265297E-3</v>
       </c>
       <c r="H4" s="1">
-        <v>1.0013217447030001E-5</v>
+        <v>2.1027756638763E-4</v>
       </c>
       <c r="I4" s="1">
-        <v>4.9859147907162197E-5</v>
-      </c>
-      <c r="J4" s="1">
-        <v>1.8663912702658001E-4</v>
+        <v>6.4816892279310004E-4</v>
+      </c>
+      <c r="J4">
+        <v>1.6610882305366399E-2</v>
       </c>
       <c r="K4" s="1">
-        <v>8.0139442630176503E-5</v>
+        <v>5.7099352874000002E-4</v>
       </c>
       <c r="L4">
-        <v>3.5879650980464401E-3</v>
-      </c>
-      <c r="M4" s="1">
-        <v>6.2239372627123898E-5</v>
+        <v>0.41970890442546399</v>
+      </c>
+      <c r="M4">
+        <v>3.8121615734113398E-3</v>
       </c>
       <c r="N4" s="1">
-        <v>5.9246970998607699E-5</v>
-      </c>
-      <c r="O4" s="1">
-        <v>7.8617897364334895E-5</v>
+        <v>9.0845355531198003E-4</v>
+      </c>
+      <c r="O4">
+        <v>3.8129680221702399E-3</v>
       </c>
       <c r="P4" s="1">
-        <v>8.74431619447359E-6</v>
-      </c>
-      <c r="Q4" s="1">
-        <v>1.11316428078455E-5</v>
-      </c>
-      <c r="R4" s="1">
-        <v>9.7600000000000001E-5</v>
-      </c>
-      <c r="S4" s="1">
-        <v>1.65897E-4</v>
-      </c>
-      <c r="T4" s="1">
-        <v>2.9600000000000001E-5</v>
+        <v>2.1860790486183E-4</v>
+      </c>
+      <c r="Q4">
+        <v>1.0575060667453299E-3</v>
+      </c>
+      <c r="R4">
+        <v>7.6814580000000004E-3</v>
+      </c>
+      <c r="S4">
+        <v>1.1124321E-2</v>
+      </c>
+      <c r="T4">
+        <v>1.6415749999999999E-3</v>
       </c>
       <c r="U4">
-        <v>4.3867289999999998E-3</v>
-      </c>
-      <c r="V4" s="1">
-        <v>1.5449600000000001E-4</v>
+        <v>0.26917912799999999</v>
+      </c>
+      <c r="V4">
+        <v>7.0896420000000002E-3</v>
       </c>
       <c r="W4">
-        <v>2.4241390000000001E-3</v>
-      </c>
-      <c r="X4" s="1">
-        <v>2.0409697829052001E-4</v>
+        <v>0.30447917600000002</v>
+      </c>
+      <c r="X4">
+        <v>1.7423436778275399E-2</v>
       </c>
       <c r="Y4" s="1">
-        <v>8.8122807945152297E-6</v>
+        <v>6.8735790197217998E-4</v>
       </c>
       <c r="Z4" s="1">
-        <v>3.4237781391765797E-5</v>
-      </c>
-      <c r="AA4" s="1">
-        <v>5.6329142445135401E-5</v>
-      </c>
-      <c r="AB4" s="1">
-        <v>4.7028994397415002E-4</v>
+        <v>7.5323119061883998E-4</v>
+      </c>
+      <c r="AA4">
+        <v>1.94898832860168E-3</v>
+      </c>
+      <c r="AB4">
+        <v>1.3617960986382001E-2</v>
       </c>
       <c r="AC4" s="1">
-        <v>3.73706042826712E-5</v>
-      </c>
-      <c r="AD4" s="1">
-        <v>1.6111996276337999E-4</v>
-      </c>
-      <c r="AE4" s="1">
-        <v>2.4682919419760998E-4</v>
-      </c>
-      <c r="AF4" s="1">
-        <v>2.0062595297327599E-5</v>
+        <v>8.0346799207742996E-4</v>
+      </c>
+      <c r="AD4">
+        <v>7.7516604307273597E-3</v>
+      </c>
+      <c r="AE4">
+        <v>1.7420445052023999E-2</v>
+      </c>
+      <c r="AF4">
+        <v>2.56801219805794E-3</v>
       </c>
       <c r="AG4" s="1">
-        <v>1.7099716999683601E-5</v>
-      </c>
-      <c r="AH4" s="1">
-        <v>3.2711808963035603E-5</v>
-      </c>
-      <c r="AI4" s="1">
-        <v>9.2353158478019893E-5</v>
-      </c>
-      <c r="AJ4" s="1">
-        <v>1.84331797235023E-5</v>
-      </c>
-      <c r="AK4" s="1">
-        <v>1.3395647902835999E-4</v>
+        <v>4.8734193449098001E-4</v>
+      </c>
+      <c r="AH4">
+        <v>4.05626431141642E-3</v>
+      </c>
+      <c r="AI4">
+        <v>9.6739933505725802E-3</v>
+      </c>
+      <c r="AJ4">
+        <v>1.56682027649769E-3</v>
+      </c>
+      <c r="AK4">
+        <v>8.0225046884767597E-3</v>
       </c>
     </row>
     <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="1">
-        <v>3.8680604577849E-4</v>
+        <v>54</v>
+      </c>
+      <c r="B5">
+        <v>5.1058398042761396E-3</v>
       </c>
       <c r="C5" s="1">
-        <v>1.1620045635088E-4</v>
-      </c>
-      <c r="D5" s="1">
-        <v>1.8813436556388499E-5</v>
-      </c>
-      <c r="E5" s="1">
-        <v>5.0371708469394E-4</v>
+        <v>8.9791261725682004E-4</v>
+      </c>
+      <c r="D5">
+        <v>1.72707347587647E-2</v>
+      </c>
+      <c r="E5">
+        <v>3.3175849371222099E-3</v>
       </c>
       <c r="F5">
-        <v>2.81949050440312E-3</v>
-      </c>
-      <c r="G5" s="1">
-        <v>3.5256269005331999E-4</v>
-      </c>
-      <c r="H5">
-        <v>4.0353266311531199E-3</v>
-      </c>
-      <c r="I5">
-        <v>4.9859147907162201E-3</v>
-      </c>
-      <c r="J5" s="1">
-        <v>1.2442608468439E-4</v>
-      </c>
-      <c r="K5" s="1">
-        <v>1.0017430328772E-5</v>
-      </c>
-      <c r="L5" s="1">
-        <v>2.213654559206E-4</v>
-      </c>
-      <c r="M5" s="1">
-        <v>3.1119686313561902E-5</v>
-      </c>
-      <c r="N5" s="1">
-        <v>3.3573283565876998E-4</v>
-      </c>
-      <c r="O5" s="1">
-        <v>1.179268460465E-4</v>
+        <v>1.1302803343642401E-3</v>
+      </c>
+      <c r="G5">
+        <v>5.7511788814948598E-3</v>
+      </c>
+      <c r="H5" s="1">
+        <v>5.2068730724555998E-4</v>
+      </c>
+      <c r="I5" s="1">
+        <v>4.1133797023407999E-4</v>
+      </c>
+      <c r="J5">
+        <v>1.03024798118677E-2</v>
+      </c>
+      <c r="K5">
+        <v>1.34233566405545E-3</v>
+      </c>
+      <c r="L5">
+        <v>3.3767455588555401E-2</v>
+      </c>
+      <c r="M5">
+        <v>8.2933964025642595E-3</v>
+      </c>
+      <c r="N5">
+        <v>1.65891518796101E-3</v>
+      </c>
+      <c r="O5">
+        <v>1.14978674895339E-2</v>
       </c>
       <c r="P5" s="1">
-        <v>6.3833508219657005E-4</v>
+        <v>9.0066456803077999E-4</v>
       </c>
       <c r="Q5" s="1">
-        <v>9.6845292428255996E-4</v>
-      </c>
-      <c r="R5" s="1">
-        <v>3.5803400000000002E-4</v>
-      </c>
-      <c r="S5" s="1">
-        <v>4.6100000000000002E-5</v>
-      </c>
-      <c r="T5" s="1">
-        <v>8.8700000000000001E-5</v>
-      </c>
-      <c r="U5" s="1">
-        <v>2.05E-5</v>
-      </c>
-      <c r="V5" s="1">
-        <v>1.3732999999999999E-4</v>
-      </c>
-      <c r="W5" s="1">
-        <v>2.44E-5</v>
-      </c>
-      <c r="X5" s="1">
-        <v>2.4706476319378998E-4</v>
+        <v>4.4526571231381999E-4</v>
+      </c>
+      <c r="R5">
+        <v>8.8423570000000003E-3</v>
+      </c>
+      <c r="S5">
+        <v>1.5207233000000001E-2</v>
+      </c>
+      <c r="T5">
+        <v>3.0908929999999999E-3</v>
+      </c>
+      <c r="U5">
+        <v>0.29037481900000001</v>
+      </c>
+      <c r="V5">
+        <v>1.6685549000000001E-2</v>
+      </c>
+      <c r="W5">
+        <v>0.44331290899999998</v>
+      </c>
+      <c r="X5">
+        <v>6.7781680684906396E-3</v>
       </c>
       <c r="Y5" s="1">
-        <v>4.4061403972576098E-5</v>
+        <v>8.6360351786248998E-4</v>
       </c>
       <c r="Z5" s="1">
-        <v>2.5678336043824298E-5</v>
-      </c>
-      <c r="AA5" s="1">
-        <v>6.9848136631966995E-4</v>
-      </c>
-      <c r="AB5" s="1">
-        <v>1.2268433321064001E-4</v>
+        <v>6.6763673713943E-4</v>
+      </c>
+      <c r="AA5">
+        <v>3.0305078635482802E-3</v>
+      </c>
+      <c r="AB5">
+        <v>6.56361182676972E-3</v>
       </c>
       <c r="AC5">
-        <v>2.2515789080309401E-3</v>
-      </c>
-      <c r="AD5" s="1">
-        <v>1.6111996276337999E-4</v>
-      </c>
-      <c r="AE5" s="1">
-        <v>6.6454013822434799E-5</v>
-      </c>
-      <c r="AF5" s="1">
-        <v>1.0031297648663799E-5</v>
-      </c>
-      <c r="AG5" s="1">
-        <v>5.1299150999050901E-5</v>
-      </c>
-      <c r="AH5" s="1">
-        <v>1.1994329953113E-4</v>
-      </c>
-      <c r="AI5" s="1">
-        <v>1.3852973771701999E-4</v>
-      </c>
-      <c r="AJ5" s="1">
-        <v>3.5023041474653999E-4</v>
-      </c>
-      <c r="AK5" s="1">
-        <v>1.0418837257762E-4</v>
+        <v>1.81247430770955E-3</v>
+      </c>
+      <c r="AD5">
+        <v>3.7952702339819899E-3</v>
+      </c>
+      <c r="AE5">
+        <v>1.2388926862611E-2</v>
+      </c>
+      <c r="AF5">
+        <v>3.8720808923842298E-3</v>
+      </c>
+      <c r="AG5">
+        <v>1.9066184454647199E-3</v>
+      </c>
+      <c r="AH5">
+        <v>7.3274452077199802E-3</v>
+      </c>
+      <c r="AI5">
+        <v>1.50766531215367E-2</v>
+      </c>
+      <c r="AJ5">
+        <v>2.3410138248847901E-3</v>
+      </c>
+      <c r="AK5">
+        <v>8.42437412556187E-3</v>
       </c>
     </row>
     <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B6">
-        <v>2.2144646120818802E-3</v>
+        <v>1.4892032762472E-3</v>
       </c>
       <c r="C6" s="1">
-        <v>1.05636778500802E-5</v>
-      </c>
-      <c r="D6" s="1">
-        <v>6.5847027947359997E-5</v>
+        <v>3.5916504690271998E-4</v>
+      </c>
+      <c r="D6">
+        <v>1.44957528666973E-2</v>
       </c>
       <c r="E6">
-        <v>1.1463906065448399E-3</v>
+        <v>2.8486069617175E-3</v>
       </c>
       <c r="F6">
-        <v>1.0495460247668001E-2</v>
+        <v>2.43693408354137E-2</v>
       </c>
       <c r="G6">
-        <v>1.30007491957163E-3</v>
-      </c>
-      <c r="H6">
-        <v>1.0674089798534001E-2</v>
-      </c>
-      <c r="I6">
-        <v>1.93328846010021E-2</v>
-      </c>
-      <c r="J6" s="1">
-        <v>2.6129477783722E-4</v>
+        <v>2.31369265347494E-3</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1.2015860936435999E-4</v>
+      </c>
+      <c r="I6" s="1">
+        <v>7.6035200558421999E-4</v>
+      </c>
+      <c r="J6">
+        <v>6.4452711866515699E-3</v>
       </c>
       <c r="K6" s="1">
-        <v>4.0069721315088197E-5</v>
-      </c>
-      <c r="L6" s="1">
-        <v>4.6117803316792398E-5</v>
-      </c>
-      <c r="M6" s="1">
-        <v>1.4003858841102001E-4</v>
-      </c>
-      <c r="N6" s="1">
-        <v>7.7021062298190002E-4</v>
-      </c>
-      <c r="O6" s="1">
-        <v>2.7516264077516998E-4</v>
+        <v>8.9155129926071005E-4</v>
+      </c>
+      <c r="L6">
+        <v>5.6374402774446997E-2</v>
+      </c>
+      <c r="M6">
+        <v>4.9635899670131302E-3</v>
+      </c>
+      <c r="N6">
+        <v>5.5287298436867402E-2</v>
+      </c>
+      <c r="O6">
+        <v>7.2525010318598999E-3</v>
       </c>
       <c r="P6" s="1">
-        <v>6.7331234697446004E-4</v>
-      </c>
-      <c r="Q6">
-        <v>2.02595899102789E-3</v>
+        <v>4.4596012591815E-4</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>8.5713649620410004E-4</v>
       </c>
       <c r="R6">
-        <v>1.0198550000000001E-3</v>
-      </c>
-      <c r="S6" s="1">
-        <v>9.2200000000000005E-5</v>
+        <v>1.3127919999999999E-3</v>
+      </c>
+      <c r="S6">
+        <v>3.9262309999999996E-3</v>
       </c>
       <c r="T6" s="1">
-        <v>2.0704499999999999E-4</v>
+        <v>5.6198100000000003E-4</v>
       </c>
       <c r="U6" s="1">
-        <v>7.1699999999999995E-5</v>
-      </c>
-      <c r="V6" s="1">
-        <v>1.7200000000000001E-5</v>
+        <v>1.02494E-4</v>
+      </c>
+      <c r="V6">
+        <v>2.1114430000000002E-3</v>
       </c>
       <c r="W6" s="1">
-        <v>2.44E-5</v>
+        <v>1.7054200000000001E-4</v>
       </c>
       <c r="X6">
-        <v>2.9970029970029901E-3</v>
+        <v>1.0097429452268099E-3</v>
       </c>
       <c r="Y6" s="1">
-        <v>6.3448421720509001E-4</v>
+        <v>2.5555614304093998E-4</v>
       </c>
       <c r="Z6" s="1">
-        <v>1.7118890695881999E-4</v>
+        <v>3.6805614996147999E-4</v>
       </c>
       <c r="AA6">
-        <v>4.1458248839619603E-3</v>
+        <v>1.08827903204001E-2</v>
       </c>
       <c r="AB6">
-        <v>2.14697583118635E-3</v>
-      </c>
-      <c r="AC6">
-        <v>8.9128891214170902E-3</v>
-      </c>
-      <c r="AD6">
-        <v>4.7082833563078397E-3</v>
-      </c>
-      <c r="AE6" s="1">
-        <v>2.5632262474367001E-4</v>
+        <v>2.4741340530814201E-3</v>
+      </c>
+      <c r="AC6" s="1">
+        <v>3.0830748533203E-4</v>
+      </c>
+      <c r="AD6" s="1">
+        <v>9.3091534041066996E-4</v>
+      </c>
+      <c r="AE6">
+        <v>1.73729778992936E-3</v>
       </c>
       <c r="AF6" s="1">
-        <v>7.0219083540646799E-5</v>
+        <v>5.7178396597382997E-4</v>
       </c>
       <c r="AG6" s="1">
-        <v>6.8398867998734606E-5</v>
-      </c>
-      <c r="AH6" s="1">
-        <v>3.5982989859339001E-4</v>
-      </c>
-      <c r="AI6" s="1">
-        <v>3.2323605467305999E-4</v>
+        <v>7.6948726498576002E-4</v>
+      </c>
+      <c r="AH6">
+        <v>2.3705157561879801E-2</v>
+      </c>
+      <c r="AI6">
+        <v>3.6479497598817801E-3</v>
       </c>
       <c r="AJ6" s="1">
-        <v>9.0322580645161004E-4</v>
-      </c>
-      <c r="AK6" s="1">
-        <v>2.8279701128211001E-4</v>
+        <v>3.7788018433178999E-4</v>
+      </c>
+      <c r="AK6">
+        <v>1.7712023338195401E-3</v>
       </c>
     </row>
     <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="B7">
-        <v>1.40217191594704E-3</v>
+        <v>1.4118420670915001E-3</v>
       </c>
       <c r="C7" s="1">
-        <v>7.9227583875601999E-4</v>
+        <v>2.1127355700160501E-5</v>
       </c>
       <c r="D7" s="1">
-        <v>9.4067182781942802E-6</v>
+        <v>2.5398139351124E-4</v>
       </c>
       <c r="E7">
-        <v>1.12902105190022E-3</v>
-      </c>
-      <c r="F7" s="1">
-        <v>2.7325458632981002E-4</v>
-      </c>
-      <c r="G7" s="1">
-        <v>3.0849235379665002E-4</v>
-      </c>
-      <c r="H7" s="1">
-        <v>3.0039652341090198E-5</v>
-      </c>
-      <c r="I7" s="1">
-        <v>1.24647869767905E-5</v>
-      </c>
-      <c r="J7" s="1">
-        <v>2.8617999477410002E-4</v>
+        <v>1.9801292294865502E-3</v>
+      </c>
+      <c r="F7">
+        <v>6.7444200171405096E-3</v>
+      </c>
+      <c r="G7">
+        <v>1.30007491957163E-3</v>
+      </c>
+      <c r="H7">
+        <v>1.99162895021428E-2</v>
+      </c>
+      <c r="I7">
+        <v>2.1090419564729599E-2</v>
+      </c>
+      <c r="J7">
+        <v>3.9567494929637001E-3</v>
       </c>
       <c r="K7" s="1">
-        <v>7.0122012301404406E-5</v>
-      </c>
-      <c r="L7" s="1">
-        <v>9.2235606633584807E-6</v>
-      </c>
-      <c r="M7" s="1">
-        <v>1.0891890209745999E-4</v>
-      </c>
-      <c r="N7" s="1">
-        <v>2.9623485499303799E-5</v>
-      </c>
-      <c r="O7" s="1">
-        <v>9.8272371705418707E-5</v>
-      </c>
-      <c r="P7" s="1">
-        <v>8.74431619447359E-6</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>1.11316428078455E-5</v>
+        <v>7.8135956564421996E-4</v>
+      </c>
+      <c r="L7">
+        <v>3.7447656293235401E-3</v>
+      </c>
+      <c r="M7">
+        <v>3.1275284745129698E-3</v>
+      </c>
+      <c r="N7">
+        <v>2.0588322422016098E-2</v>
+      </c>
+      <c r="O7">
+        <v>5.6801430845732004E-3</v>
+      </c>
+      <c r="P7">
+        <v>6.0475690800979302E-2</v>
+      </c>
+      <c r="Q7">
+        <v>0.12070040296546899</v>
       </c>
       <c r="R7" s="1">
-        <v>5.6417499999999998E-4</v>
-      </c>
-      <c r="S7" s="1">
-        <v>1.4746400000000001E-4</v>
+        <v>8.3541300000000002E-4</v>
+      </c>
+      <c r="S7">
+        <v>3.262643E-3</v>
       </c>
       <c r="T7" s="1">
-        <v>1.18312E-4</v>
-      </c>
-      <c r="U7">
-        <v>2.5725909999999999E-3</v>
-      </c>
-      <c r="V7" s="1">
-        <v>1.2016299999999999E-4</v>
+        <v>2.9577899999999997E-4</v>
+      </c>
+      <c r="U7" s="1">
+        <v>4.1E-5</v>
+      </c>
+      <c r="V7">
+        <v>1.459127E-3</v>
       </c>
       <c r="W7" s="1">
-        <v>4.9944599999999996E-4</v>
-      </c>
-      <c r="X7">
-        <v>1.7509372348081999E-3</v>
-      </c>
-      <c r="Y7">
-        <v>1.8770158092317401E-3</v>
-      </c>
-      <c r="Z7">
-        <v>1.88307797654711E-3</v>
-      </c>
-      <c r="AA7" s="1">
-        <v>4.9569645351718995E-4</v>
-      </c>
-      <c r="AB7">
-        <v>1.61534372060687E-3</v>
-      </c>
-      <c r="AC7" s="1">
-        <v>2.1488097462534999E-4</v>
+        <v>2.6799499999999998E-4</v>
+      </c>
+      <c r="X7" s="1">
+        <v>5.2635536506503999E-4</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>2.0268245827385E-4</v>
+      </c>
+      <c r="Z7" s="1">
+        <v>9.4153898827356E-5</v>
+      </c>
+      <c r="AA7">
+        <v>1.0927853634356199E-3</v>
+      </c>
+      <c r="AB7" s="1">
+        <v>6.9521122152701E-4</v>
+      </c>
+      <c r="AC7">
+        <v>1.2986284988228201E-3</v>
       </c>
       <c r="AD7" s="1">
-        <v>9.4881755849549E-4</v>
-      </c>
-      <c r="AE7" s="1">
-        <v>2.9429634692791997E-4</v>
+        <v>5.5496876062944005E-4</v>
+      </c>
+      <c r="AE7">
+        <v>1.5948963317384301E-3</v>
       </c>
       <c r="AF7" s="1">
-        <v>2.3071984591926001E-4</v>
+        <v>1.3040686943262001E-4</v>
       </c>
       <c r="AG7" s="1">
         <v>2.6504561349509001E-4</v>
       </c>
-      <c r="AH7" s="1">
-        <v>1.6355904481516999E-4</v>
-      </c>
-      <c r="AI7" s="1">
-        <v>4.8485408200960001E-4</v>
-      </c>
-      <c r="AJ7" s="1">
-        <v>2.7649769585253399E-5</v>
-      </c>
-      <c r="AK7" s="1">
-        <v>1.1907242580299E-4</v>
+      <c r="AH7">
+        <v>1.8754770472140399E-3</v>
+      </c>
+      <c r="AI7">
+        <v>1.59309198374584E-3</v>
+      </c>
+      <c r="AJ7">
+        <v>2.8571428571428502E-3</v>
+      </c>
+      <c r="AK7">
+        <v>1.05676777900157E-3</v>
       </c>
     </row>
     <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="1">
-        <v>3.8680604577849503E-5</v>
-      </c>
-      <c r="C8" s="1">
-        <v>2.1127355700160501E-5</v>
+        <v>49</v>
+      </c>
+      <c r="B8">
+        <v>3.2878513891172099E-3</v>
+      </c>
+      <c r="C8">
+        <v>1.59511535536212E-3</v>
       </c>
       <c r="D8" s="1">
-        <v>9.4067182781942802E-6</v>
-      </c>
-      <c r="E8" s="1">
-        <v>1.7369554644618901E-5</v>
-      </c>
-      <c r="F8" s="1">
-        <v>3.72619890449752E-5</v>
-      </c>
-      <c r="G8" s="1">
-        <v>8.8140672513331204E-5</v>
+        <v>8.4660464503747996E-4</v>
+      </c>
+      <c r="E8">
+        <v>1.61536858194955E-3</v>
+      </c>
+      <c r="F8">
+        <v>1.1302803343642401E-3</v>
+      </c>
+      <c r="G8">
+        <v>1.23396941518663E-3</v>
       </c>
       <c r="H8" s="1">
         <v>6.0079304682180397E-5</v>
       </c>
       <c r="I8" s="1">
-        <v>1.9943659162864001E-4</v>
-      </c>
-      <c r="J8" s="1">
-        <v>1.4931130162126999E-4</v>
-      </c>
-      <c r="K8" s="1">
-        <v>1.0017430328772E-5</v>
+        <v>7.4788721860743397E-5</v>
+      </c>
+      <c r="J8">
+        <v>3.0982095086413901E-3</v>
+      </c>
+      <c r="K8">
+        <v>1.4324925370144E-3</v>
       </c>
       <c r="L8" s="1">
-        <v>9.2235606633584807E-6</v>
-      </c>
-      <c r="M8" s="1">
-        <v>2.3339764735171001E-4</v>
+        <v>3.3204818388090003E-4</v>
+      </c>
+      <c r="M8">
+        <v>2.0538992966950801E-3</v>
       </c>
       <c r="N8" s="1">
-        <v>2.3698788399443001E-4</v>
-      </c>
-      <c r="O8" s="1">
-        <v>3.3412606379842002E-4</v>
+        <v>7.5046163264902996E-4</v>
+      </c>
+      <c r="O8">
+        <v>1.4347766268991099E-3</v>
       </c>
       <c r="P8" s="1">
-        <v>7.5201119272471999E-4</v>
-      </c>
-      <c r="Q8">
-        <v>1.52503506467484E-3</v>
-      </c>
-      <c r="R8" s="1">
-        <v>4.3399999999999998E-5</v>
-      </c>
-      <c r="S8" s="1">
-        <v>1.75114E-4</v>
-      </c>
-      <c r="T8" s="1">
-        <v>2.9600000000000001E-5</v>
+        <v>5.2465897166841503E-5</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>8.9053142462764597E-5</v>
+      </c>
+      <c r="R8">
+        <v>1.551481E-3</v>
+      </c>
+      <c r="S8">
+        <v>2.3041260000000001E-3</v>
+      </c>
+      <c r="T8">
+        <v>2.3958118E-2</v>
       </c>
       <c r="U8" s="1">
-        <v>1.0200000000000001E-5</v>
-      </c>
-      <c r="V8" s="1">
-        <v>2.7465900000000001E-4</v>
+        <v>1.9473799999999999E-4</v>
+      </c>
+      <c r="V8">
+        <v>4.8837848000000003E-2</v>
       </c>
       <c r="W8" s="1">
-        <v>6.0900000000000003E-5</v>
-      </c>
-      <c r="X8" s="1">
-        <v>4.29677849032687E-5</v>
+        <v>2.92358E-4</v>
+      </c>
+      <c r="X8">
+        <v>4.8768435865209998E-3</v>
       </c>
       <c r="Y8" s="1">
-        <v>8.8122807945152297E-6</v>
+        <v>3.1724210860254002E-4</v>
       </c>
       <c r="Z8" s="1">
-        <v>8.5594453479414492E-6</v>
-      </c>
-      <c r="AA8" s="1">
-        <v>4.5063313956108302E-5</v>
-      </c>
-      <c r="AB8" s="1">
-        <v>1.0223694434219999E-4</v>
+        <v>1.6262946161087999E-4</v>
+      </c>
+      <c r="AA8">
+        <v>1.3293677617051899E-3</v>
+      </c>
+      <c r="AB8">
+        <v>3.3329243855559601E-3</v>
       </c>
       <c r="AC8" s="1">
-        <v>2.8962218319069998E-4</v>
-      </c>
-      <c r="AD8" s="1">
-        <v>1.4321774467856001E-4</v>
-      </c>
-      <c r="AE8" s="1">
-        <v>6.6454013822434799E-5</v>
-      </c>
-      <c r="AF8" s="1">
-        <v>1.9059465532460999E-4</v>
+        <v>6.3530027280540998E-4</v>
+      </c>
+      <c r="AD8">
+        <v>2.6137238403838199E-3</v>
+      </c>
+      <c r="AE8">
+        <v>6.2656641604010004E-3</v>
+      </c>
+      <c r="AF8">
+        <v>1.39435037316427E-3</v>
       </c>
       <c r="AG8" s="1">
-        <v>9.4048443498260094E-5</v>
-      </c>
-      <c r="AH8" s="1">
-        <v>2.1807872642023001E-4</v>
-      </c>
-      <c r="AI8" s="1">
-        <v>1.8470631695603E-4</v>
+        <v>1.8809688699652E-4</v>
+      </c>
+      <c r="AH8">
+        <v>2.2571148184494598E-3</v>
+      </c>
+      <c r="AI8">
+        <v>3.6479497598817801E-3</v>
       </c>
       <c r="AJ8" s="1">
-        <v>9.6774193548386999E-4</v>
-      </c>
-      <c r="AK8" s="1">
-        <v>8.1862292739558E-4</v>
+        <v>3.7788018433178999E-4</v>
+      </c>
+      <c r="AK8">
+        <v>4.9117375643735299E-3</v>
       </c>
     </row>
     <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B9">
-        <v>1.54722418311398E-3</v>
+        <v>1.4892032762472E-3</v>
       </c>
       <c r="C9" s="1">
-        <v>2.7465562410208003E-4</v>
+        <v>8.4509422800642194E-5</v>
       </c>
       <c r="D9" s="1">
-        <v>7.7135089881193001E-4</v>
-      </c>
-      <c r="E9">
-        <v>2.9354547349405898E-3</v>
+        <v>4.1389560424053999E-4</v>
+      </c>
+      <c r="E9" s="1">
+        <v>9.5532550545403998E-4</v>
       </c>
       <c r="F9" s="1">
-        <v>3.1051657537479001E-4</v>
-      </c>
-      <c r="G9">
-        <v>1.85095412277995E-3</v>
+        <v>1.8630994522487001E-4</v>
+      </c>
+      <c r="G9" s="1">
+        <v>9.6954739764663997E-4</v>
       </c>
       <c r="H9" s="1">
-        <v>1.3017182681138999E-4</v>
-      </c>
-      <c r="I9" s="1">
-        <v>6.2323934883952797E-5</v>
-      </c>
-      <c r="J9" s="1">
-        <v>2.9862260324253997E-4</v>
+        <v>1.9025113149357E-4</v>
+      </c>
+      <c r="I9">
+        <v>5.1192880113678799E-2</v>
+      </c>
+      <c r="J9">
+        <v>2.1028008311662402E-3</v>
       </c>
       <c r="K9" s="1">
-        <v>4.0069721315088197E-5</v>
-      </c>
-      <c r="L9" s="1">
-        <v>2.76706819900754E-5</v>
-      </c>
-      <c r="M9" s="1">
-        <v>4.5123545154664E-4</v>
-      </c>
-      <c r="N9" s="1">
-        <v>5.9246970998607699E-5</v>
-      </c>
-      <c r="O9" s="1">
-        <v>1.5723579472866E-4</v>
+        <v>1.2020916394526E-4</v>
+      </c>
+      <c r="L9">
+        <v>1.2544042502167501E-3</v>
+      </c>
+      <c r="M9">
+        <v>2.1472583556357699E-3</v>
+      </c>
+      <c r="N9">
+        <v>1.8662795864561399E-3</v>
+      </c>
+      <c r="O9">
+        <v>1.61166689596886E-3</v>
       </c>
       <c r="P9" s="1">
-        <v>8.74431619447359E-6</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>3.3394928423536698E-5</v>
+        <v>2.0111927247288999E-4</v>
+      </c>
+      <c r="Q9">
+        <v>8.7995636396019303E-2</v>
       </c>
       <c r="R9">
-        <v>1.4429860000000001E-3</v>
-      </c>
-      <c r="S9" s="1">
-        <v>3.8709299999999997E-4</v>
+        <v>2.1807530000000001E-3</v>
+      </c>
+      <c r="S9">
+        <v>3.5575709999999998E-3</v>
       </c>
       <c r="T9" s="1">
-        <v>3.8451300000000001E-4</v>
+        <v>7.0987000000000003E-4</v>
       </c>
       <c r="U9" s="1">
-        <v>1.9473799999999999E-4</v>
-      </c>
-      <c r="V9" s="1">
-        <v>1.8882799999999999E-4</v>
+        <v>6.1500000000000004E-5</v>
+      </c>
+      <c r="V9">
+        <v>1.7337870000000001E-3</v>
       </c>
       <c r="W9" s="1">
-        <v>6.0900000000000003E-5</v>
+        <v>2.43632E-4</v>
       </c>
       <c r="X9">
-        <v>1.91206642819546E-3</v>
+        <v>1.31051743954969E-3</v>
       </c>
       <c r="Y9" s="1">
-        <v>8.5479123706797E-4</v>
-      </c>
-      <c r="Z9">
-        <v>1.10331250534965E-2</v>
+        <v>7.4904386753379005E-4</v>
+      </c>
+      <c r="Z9" s="1">
+        <v>2.2254557904647E-4</v>
       </c>
       <c r="AA9" s="1">
-        <v>7.6607633725383996E-4</v>
+        <v>3.1544319769275002E-4</v>
       </c>
       <c r="AB9">
-        <v>3.5537561853351302E-2</v>
+        <v>2.3718971087392099E-3</v>
       </c>
       <c r="AC9" s="1">
-        <v>2.4290892783735999E-4</v>
+        <v>4.5778990246272001E-4</v>
       </c>
       <c r="AD9">
-        <v>1.2710574840222701E-3</v>
-      </c>
-      <c r="AE9" s="1">
-        <v>2.9429634692791997E-4</v>
+        <v>4.70470291269088E-2</v>
+      </c>
+      <c r="AE9">
+        <v>2.13602187286397E-3</v>
       </c>
       <c r="AF9" s="1">
-        <v>1.6050076237862E-4</v>
-      </c>
-      <c r="AG9">
-        <v>2.1973136344593499E-3</v>
+        <v>7.2225343070378997E-4</v>
+      </c>
+      <c r="AG9" s="1">
+        <v>4.7024221749129998E-4</v>
       </c>
       <c r="AH9" s="1">
-        <v>1.8536691745719999E-4</v>
+        <v>8.8321884200195998E-4</v>
       </c>
       <c r="AI9">
-        <v>3.2554488363501998E-3</v>
+        <v>2.0779460657554399E-3</v>
       </c>
       <c r="AJ9" s="1">
-        <v>1.1059907834101001E-4</v>
-      </c>
-      <c r="AK9" s="1">
-        <v>3.4233322418360002E-4</v>
+        <v>6.6359447004607996E-4</v>
+      </c>
+      <c r="AK9">
+        <v>5.8166880004762798E-2</v>
       </c>
     </row>
     <row r="10" spans="1:37" x14ac:dyDescent="0.2">
@@ -1710,1019 +1714,1019 @@
     </row>
     <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>46</v>
-      </c>
-      <c r="B11" s="1">
-        <v>5.4152846408988999E-4</v>
+        <v>52</v>
+      </c>
+      <c r="B11">
+        <v>4.9124367813868901E-3</v>
       </c>
       <c r="C11" s="1">
-        <v>4.8592918110369E-4</v>
+        <v>1.584551677512E-4</v>
       </c>
       <c r="D11" s="1">
-        <v>1.3169405589471999E-4</v>
+        <v>4.4211575907512999E-4</v>
       </c>
       <c r="E11">
-        <v>1.8411727923296E-3</v>
+        <v>3.2654762731883502E-3</v>
       </c>
       <c r="F11">
-        <v>1.7388928220988401E-3</v>
-      </c>
-      <c r="G11" s="1">
-        <v>5.5087920320831996E-4</v>
+        <v>6.6276657847995898E-2</v>
+      </c>
+      <c r="G11">
+        <v>3.21713454673659E-3</v>
       </c>
       <c r="H11" s="1">
-        <v>2.0026434894060099E-5</v>
+        <v>1.5019826170545E-4</v>
       </c>
       <c r="I11" s="1">
-        <v>1.7450701767506E-4</v>
-      </c>
-      <c r="J11" s="1">
-        <v>1.9908173549501999E-4</v>
+        <v>1.9943659162864001E-4</v>
+      </c>
+      <c r="J11">
+        <v>1.65486692630243E-3</v>
       </c>
       <c r="K11" s="1">
-        <v>9.0156872958948504E-5</v>
+        <v>1.1019173361649E-4</v>
       </c>
       <c r="L11" s="1">
-        <v>9.2235606633584807E-6</v>
+        <v>2.76706819900754E-5</v>
       </c>
       <c r="M11" s="1">
-        <v>2.6451733366526998E-4</v>
-      </c>
-      <c r="N11" s="1">
-        <v>4.1472879699025E-4</v>
-      </c>
-      <c r="O11" s="1">
-        <v>1.3758132038758E-4</v>
+        <v>7.7799215783904004E-4</v>
+      </c>
+      <c r="N11">
+        <v>1.9472504468209001E-2</v>
+      </c>
+      <c r="O11">
+        <v>2.5354271899998E-3</v>
       </c>
       <c r="P11" s="1">
-        <v>8.74431619447359E-6</v>
+        <v>1.8363064008394001E-4</v>
       </c>
       <c r="Q11" s="1">
-        <v>4.4526571231382298E-5</v>
-      </c>
-      <c r="R11" s="1">
-        <v>8.8966000000000002E-4</v>
-      </c>
-      <c r="S11" s="1">
-        <v>2.30413E-4</v>
+        <v>2.2263285615691098E-5</v>
+      </c>
+      <c r="R11">
+        <v>2.734078E-3</v>
+      </c>
+      <c r="S11">
+        <v>1.5207230000000001E-3</v>
       </c>
       <c r="T11" s="1">
-        <v>2.5141200000000001E-4</v>
-      </c>
-      <c r="U11">
-        <v>2.7673289999999998E-3</v>
+        <v>9.3170500000000001E-4</v>
+      </c>
+      <c r="U11" s="1">
+        <v>3.4847799999999999E-4</v>
       </c>
       <c r="V11" s="1">
-        <v>1.02997E-4</v>
+        <v>7.7247899999999996E-4</v>
       </c>
       <c r="W11" s="1">
-        <v>4.2635600000000002E-4</v>
-      </c>
-      <c r="X11" s="1">
-        <v>6.6600066600066004E-4</v>
-      </c>
-      <c r="Y11">
-        <v>1.4011526463279199E-3</v>
+        <v>1.21816E-4</v>
+      </c>
+      <c r="X11">
+        <v>5.5428442525216701E-3</v>
+      </c>
+      <c r="Y11" s="1">
+        <v>4.3180175893124E-4</v>
       </c>
       <c r="Z11">
-        <v>3.8175126251818801E-3</v>
+        <v>1.1555251219720899E-3</v>
       </c>
       <c r="AA11">
-        <v>1.56595015997476E-3</v>
+        <v>4.6088504348609699E-2</v>
       </c>
       <c r="AB11">
-        <v>1.11029321555637E-2</v>
+        <v>3.6805299963194702E-3</v>
       </c>
       <c r="AC11" s="1">
-        <v>3.73706042826712E-5</v>
-      </c>
-      <c r="AD11" s="1">
-        <v>3.5804436169640998E-4</v>
-      </c>
-      <c r="AE11" s="1">
-        <v>1.6138831928305E-4</v>
+        <v>6.5398557494674001E-4</v>
+      </c>
+      <c r="AD11">
+        <v>2.8643548935713102E-3</v>
+      </c>
+      <c r="AE11">
+        <v>2.2594364699627801E-3</v>
       </c>
       <c r="AF11" s="1">
-        <v>2.0062595297327E-4</v>
-      </c>
-      <c r="AG11">
-        <v>1.0687323124802201E-3</v>
-      </c>
-      <c r="AH11" s="1">
-        <v>3.3802202595135998E-4</v>
-      </c>
-      <c r="AI11" s="1">
-        <v>8.7735500554117995E-4</v>
+        <v>7.2225343070378997E-4</v>
+      </c>
+      <c r="AG11" s="1">
+        <v>3.4199433999367002E-4</v>
+      </c>
+      <c r="AH11">
+        <v>1.5832515538109201E-2</v>
+      </c>
+      <c r="AI11">
+        <v>2.7244181751015801E-3</v>
       </c>
       <c r="AJ11" s="1">
-        <v>1.84331797235023E-5</v>
+        <v>1.4746543778801E-4</v>
       </c>
       <c r="AK11" s="1">
-        <v>1.0418837257762E-4</v>
+        <v>7.8885482094482999E-4</v>
       </c>
     </row>
     <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="1">
-        <v>2.3208362746709001E-4</v>
+        <v>59</v>
+      </c>
+      <c r="B12">
+        <v>1.15074798619102E-3</v>
       </c>
       <c r="C12" s="1">
-        <v>9.50731006507225E-5</v>
+        <v>8.2396687230625997E-4</v>
       </c>
       <c r="D12" s="1">
-        <v>9.4067182781942802E-6</v>
-      </c>
-      <c r="E12" s="1">
-        <v>1.7369554644618901E-5</v>
-      </c>
-      <c r="F12" s="1">
-        <v>3.72619890449752E-5</v>
+        <v>3.7626873112777101E-5</v>
+      </c>
+      <c r="E12">
+        <v>1.5632599180156999E-3</v>
+      </c>
+      <c r="F12">
+        <v>7.5269217870849899E-3</v>
       </c>
       <c r="G12" s="1">
-        <v>1.1017584064166E-4</v>
+        <v>7.9326605261998003E-4</v>
       </c>
       <c r="H12" s="1">
-        <v>3.0039652341090198E-5</v>
+        <v>7.0092522129210506E-5</v>
       </c>
       <c r="I12" s="1">
-        <v>2.4929573953581098E-5</v>
-      </c>
-      <c r="J12" s="1">
-        <v>1.2442608468439E-4</v>
+        <v>6.2323934883952797E-5</v>
+      </c>
+      <c r="J12">
+        <v>1.4433425823389601E-3</v>
       </c>
       <c r="K12" s="1">
-        <v>1.1019173361649E-4</v>
+        <v>5.8101095906877001E-4</v>
       </c>
       <c r="L12" s="1">
-        <v>9.2235606633584807E-6</v>
+        <v>3.1360106255417998E-4</v>
       </c>
       <c r="M12" s="1">
-        <v>3.1119686313561902E-5</v>
-      </c>
-      <c r="N12" s="1">
-        <v>9.8744951664346098E-6</v>
+        <v>9.4915043256363005E-4</v>
+      </c>
+      <c r="N12">
+        <v>4.8187536412200903E-3</v>
       </c>
       <c r="O12" s="1">
-        <v>5.8963423023251198E-5</v>
+        <v>5.3067080720925995E-4</v>
       </c>
       <c r="P12" s="1">
-        <v>8.74431619447359E-6</v>
+        <v>1.1367611052815E-4</v>
       </c>
       <c r="Q12" s="1">
-        <v>1.11316428078455E-5</v>
+        <v>4.4526571231382298E-5</v>
       </c>
       <c r="R12" s="1">
-        <v>9.7600000000000001E-5</v>
+        <v>4.0143200000000001E-4</v>
       </c>
       <c r="S12" s="1">
-        <v>9.2200000000000005E-5</v>
+        <v>5.6220700000000001E-4</v>
       </c>
       <c r="T12" s="1">
-        <v>1.4800000000000001E-5</v>
+        <v>3.2535700000000002E-4</v>
       </c>
       <c r="U12" s="1">
-        <v>7.7895199999999996E-4</v>
+        <v>2.5623399999999999E-4</v>
       </c>
       <c r="V12" s="1">
-        <v>8.5799999999999998E-5</v>
+        <v>7.2098099999999999E-4</v>
       </c>
       <c r="W12" s="1">
-        <v>2.5581399999999999E-4</v>
-      </c>
-      <c r="X12" s="1">
-        <v>3.7596811790359999E-4</v>
-      </c>
-      <c r="Y12" s="1">
-        <v>8.7241579865699999E-4</v>
-      </c>
-      <c r="Z12" s="1">
-        <v>8.5594453479414492E-6</v>
-      </c>
-      <c r="AA12" s="1">
-        <v>1.2392411337929001E-4</v>
-      </c>
-      <c r="AB12" s="1">
-        <v>1.6357911094753001E-4</v>
+        <v>3.6544799999999999E-4</v>
+      </c>
+      <c r="X12">
+        <v>1.53609831029185E-3</v>
+      </c>
+      <c r="Y12">
+        <v>1.63908422777983E-3</v>
+      </c>
+      <c r="Z12">
+        <v>7.8746897201061299E-3</v>
+      </c>
+      <c r="AA12">
+        <v>9.7674732999864806E-3</v>
+      </c>
+      <c r="AB12">
+        <v>1.1246063877642801E-3</v>
       </c>
       <c r="AC12" s="1">
-        <v>3.73706042826712E-5</v>
-      </c>
-      <c r="AD12" s="1">
-        <v>1.790221808482E-4</v>
-      </c>
-      <c r="AE12" s="1">
-        <v>1.0442773600667999E-4</v>
-      </c>
-      <c r="AF12" s="1">
-        <v>3.0093892945991002E-4</v>
-      </c>
-      <c r="AG12" s="1">
-        <v>2.5649575499525399E-5</v>
-      </c>
-      <c r="AH12" s="1">
-        <v>1.0903936321011E-4</v>
-      </c>
-      <c r="AI12" s="1">
-        <v>1.6161802733653E-4</v>
+        <v>1.4013976606001E-4</v>
+      </c>
+      <c r="AD12">
+        <v>1.25315526593744E-3</v>
+      </c>
+      <c r="AE12">
+        <v>1.6803372066529899E-3</v>
+      </c>
+      <c r="AF12">
+        <v>1.25391220608297E-3</v>
+      </c>
+      <c r="AG12">
+        <v>4.8221201939107903E-3</v>
+      </c>
+      <c r="AH12">
+        <v>9.5409442808853905E-3</v>
+      </c>
+      <c r="AI12">
+        <v>1.6392685629848501E-3</v>
       </c>
       <c r="AJ12" s="1">
-        <v>9.21658986175115E-6</v>
-      </c>
-      <c r="AK12" s="1">
-        <v>5.9536212901497302E-5</v>
+        <v>1.0138248847926E-4</v>
+      </c>
+      <c r="AK12">
+        <v>2.1433036644538999E-3</v>
       </c>
     </row>
     <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B13">
-        <v>1.4892032762472E-3</v>
-      </c>
-      <c r="C13" s="1">
-        <v>8.4509422800642194E-5</v>
-      </c>
-      <c r="D13" s="1">
-        <v>4.1389560424053999E-4</v>
-      </c>
-      <c r="E13" s="1">
-        <v>9.5532550545403998E-4</v>
-      </c>
-      <c r="F13" s="1">
-        <v>1.8630994522487001E-4</v>
-      </c>
-      <c r="G13" s="1">
-        <v>9.6954739764663997E-4</v>
+        <v>4.9124367813868901E-3</v>
+      </c>
+      <c r="C13">
+        <v>3.5493957576269702E-3</v>
+      </c>
+      <c r="D13">
+        <v>0.31910410415118401</v>
+      </c>
+      <c r="E13">
+        <v>1.5146251650107599E-2</v>
+      </c>
+      <c r="F13">
+        <v>1.502900224814E-3</v>
+      </c>
+      <c r="G13">
+        <v>9.8056498171080995E-3</v>
       </c>
       <c r="H13" s="1">
-        <v>1.9025113149357E-4</v>
-      </c>
-      <c r="I13">
-        <v>5.1192880113678799E-2</v>
-      </c>
-      <c r="J13">
-        <v>2.1028008311662402E-3</v>
-      </c>
-      <c r="K13" s="1">
-        <v>1.2020916394526E-4</v>
+        <v>4.1054191532822998E-4</v>
+      </c>
+      <c r="I13" s="1">
+        <v>6.1077456186272997E-4</v>
+      </c>
+      <c r="J13" s="1">
+        <v>6.7190085729572E-4</v>
+      </c>
+      <c r="K13">
+        <v>1.04181275419229E-3</v>
       </c>
       <c r="L13">
-        <v>1.2544042502167501E-3</v>
+        <v>8.3593130292017898E-2</v>
       </c>
       <c r="M13">
-        <v>2.1472583556357699E-3</v>
-      </c>
-      <c r="N13">
-        <v>1.8662795864561399E-3</v>
-      </c>
-      <c r="O13">
-        <v>1.61166689596886E-3</v>
+        <v>2.7696520819070099E-3</v>
+      </c>
+      <c r="N13" s="1">
+        <v>2.2711338882798999E-4</v>
+      </c>
+      <c r="O13" s="1">
+        <v>8.8445134534875997E-4</v>
       </c>
       <c r="P13" s="1">
-        <v>2.0111927247288999E-4</v>
-      </c>
-      <c r="Q13">
-        <v>8.7995636396019303E-2</v>
+        <v>1.5739769150052E-4</v>
+      </c>
+      <c r="Q13" s="1">
+        <v>1.5584299930983001E-4</v>
       </c>
       <c r="R13">
-        <v>2.1807530000000001E-3</v>
+        <v>6.2927199999999999E-3</v>
       </c>
       <c r="S13">
-        <v>3.5575709999999998E-3</v>
-      </c>
-      <c r="T13" s="1">
-        <v>7.0987000000000003E-4</v>
-      </c>
-      <c r="U13" s="1">
-        <v>6.1500000000000004E-5</v>
+        <v>1.188929E-3</v>
+      </c>
+      <c r="T13">
+        <v>0.638868349</v>
+      </c>
+      <c r="U13">
+        <v>0.13941189100000001</v>
       </c>
       <c r="V13">
-        <v>1.7337870000000001E-3</v>
-      </c>
-      <c r="W13" s="1">
-        <v>2.43632E-4</v>
+        <v>0.24700449799999999</v>
+      </c>
+      <c r="W13">
+        <v>1.8308950000000001E-2</v>
       </c>
       <c r="X13">
-        <v>1.31051743954969E-3</v>
+        <v>6.5633291439743001E-3</v>
       </c>
       <c r="Y13" s="1">
-        <v>7.4904386753379005E-4</v>
+        <v>6.1685965561606001E-4</v>
       </c>
       <c r="Z13" s="1">
-        <v>2.2254557904647E-4</v>
-      </c>
-      <c r="AA13" s="1">
-        <v>3.1544319769275002E-4</v>
+        <v>1.1127278952323E-4</v>
+      </c>
+      <c r="AA13">
+        <v>1.2505069622819999E-3</v>
       </c>
       <c r="AB13">
-        <v>2.3718971087392099E-3</v>
+        <v>3.1693452746084298E-3</v>
       </c>
       <c r="AC13" s="1">
-        <v>4.5778990246272001E-4</v>
+        <v>6.4464292387607001E-4</v>
       </c>
       <c r="AD13">
-        <v>4.70470291269088E-2</v>
-      </c>
-      <c r="AE13">
-        <v>2.13602187286397E-3</v>
+        <v>1.79022180848207E-3</v>
+      </c>
+      <c r="AE13" s="1">
+        <v>5.9808612440190995E-4</v>
       </c>
       <c r="AF13" s="1">
-        <v>7.2225343070378997E-4</v>
+        <v>5.7178396597382997E-4</v>
       </c>
       <c r="AG13" s="1">
-        <v>4.7024221749129998E-4</v>
+        <v>5.9849009498892703E-5</v>
       </c>
       <c r="AH13" s="1">
-        <v>8.8321884200195998E-4</v>
-      </c>
-      <c r="AI13">
-        <v>2.0779460657554399E-3</v>
+        <v>3.4892596227237998E-4</v>
+      </c>
+      <c r="AI13" s="1">
+        <v>4.1558921315108002E-4</v>
       </c>
       <c r="AJ13" s="1">
-        <v>6.6359447004607996E-4</v>
-      </c>
-      <c r="AK13">
-        <v>5.8166880004762798E-2</v>
+        <v>2.3963133640552E-4</v>
+      </c>
+      <c r="AK13" s="1">
+        <v>1.7860863870449001E-4</v>
       </c>
     </row>
     <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B14">
-        <v>3.2878513891172099E-3</v>
-      </c>
-      <c r="C14">
-        <v>1.59511535536212E-3</v>
+        <v>1.54722418311398E-3</v>
+      </c>
+      <c r="C14" s="1">
+        <v>2.7465562410208003E-4</v>
       </c>
       <c r="D14" s="1">
-        <v>8.4660464503747996E-4</v>
+        <v>7.7135089881193001E-4</v>
       </c>
       <c r="E14">
-        <v>1.61536858194955E-3</v>
-      </c>
-      <c r="F14">
-        <v>1.1302803343642401E-3</v>
+        <v>2.9354547349405898E-3</v>
+      </c>
+      <c r="F14" s="1">
+        <v>3.1051657537479001E-4</v>
       </c>
       <c r="G14">
-        <v>1.23396941518663E-3</v>
+        <v>1.85095412277995E-3</v>
       </c>
       <c r="H14" s="1">
-        <v>6.0079304682180397E-5</v>
+        <v>1.3017182681138999E-4</v>
       </c>
       <c r="I14" s="1">
-        <v>7.4788721860743397E-5</v>
-      </c>
-      <c r="J14">
-        <v>3.0982095086413901E-3</v>
-      </c>
-      <c r="K14">
-        <v>1.4324925370144E-3</v>
+        <v>6.2323934883952797E-5</v>
+      </c>
+      <c r="J14" s="1">
+        <v>2.9862260324253997E-4</v>
+      </c>
+      <c r="K14" s="1">
+        <v>4.0069721315088197E-5</v>
       </c>
       <c r="L14" s="1">
-        <v>3.3204818388090003E-4</v>
-      </c>
-      <c r="M14">
-        <v>2.0538992966950801E-3</v>
+        <v>2.76706819900754E-5</v>
+      </c>
+      <c r="M14" s="1">
+        <v>4.5123545154664E-4</v>
       </c>
       <c r="N14" s="1">
-        <v>7.5046163264902996E-4</v>
-      </c>
-      <c r="O14">
-        <v>1.4347766268991099E-3</v>
+        <v>5.9246970998607699E-5</v>
+      </c>
+      <c r="O14" s="1">
+        <v>1.5723579472866E-4</v>
       </c>
       <c r="P14" s="1">
-        <v>5.2465897166841503E-5</v>
+        <v>8.74431619447359E-6</v>
       </c>
       <c r="Q14" s="1">
-        <v>8.9053142462764597E-5</v>
+        <v>3.3394928423536698E-5</v>
       </c>
       <c r="R14">
-        <v>1.551481E-3</v>
-      </c>
-      <c r="S14">
-        <v>2.3041260000000001E-3</v>
-      </c>
-      <c r="T14">
-        <v>2.3958118E-2</v>
+        <v>1.4429860000000001E-3</v>
+      </c>
+      <c r="S14" s="1">
+        <v>3.8709299999999997E-4</v>
+      </c>
+      <c r="T14" s="1">
+        <v>3.8451300000000001E-4</v>
       </c>
       <c r="U14" s="1">
         <v>1.9473799999999999E-4</v>
       </c>
-      <c r="V14">
-        <v>4.8837848000000003E-2</v>
+      <c r="V14" s="1">
+        <v>1.8882799999999999E-4</v>
       </c>
       <c r="W14" s="1">
-        <v>2.92358E-4</v>
+        <v>6.0900000000000003E-5</v>
       </c>
       <c r="X14">
-        <v>4.8768435865209998E-3</v>
+        <v>1.91206642819546E-3</v>
       </c>
       <c r="Y14" s="1">
-        <v>3.1724210860254002E-4</v>
-      </c>
-      <c r="Z14" s="1">
-        <v>1.6262946161087999E-4</v>
-      </c>
-      <c r="AA14">
-        <v>1.3293677617051899E-3</v>
+        <v>8.5479123706797E-4</v>
+      </c>
+      <c r="Z14">
+        <v>1.10331250534965E-2</v>
+      </c>
+      <c r="AA14" s="1">
+        <v>7.6607633725383996E-4</v>
       </c>
       <c r="AB14">
-        <v>3.3329243855559601E-3</v>
+        <v>3.5537561853351302E-2</v>
       </c>
       <c r="AC14" s="1">
-        <v>6.3530027280540998E-4</v>
+        <v>2.4290892783735999E-4</v>
       </c>
       <c r="AD14">
-        <v>2.6137238403838199E-3</v>
-      </c>
-      <c r="AE14">
-        <v>6.2656641604010004E-3</v>
-      </c>
-      <c r="AF14">
-        <v>1.39435037316427E-3</v>
-      </c>
-      <c r="AG14" s="1">
-        <v>1.8809688699652E-4</v>
-      </c>
-      <c r="AH14">
-        <v>2.2571148184494598E-3</v>
+        <v>1.2710574840222701E-3</v>
+      </c>
+      <c r="AE14" s="1">
+        <v>2.9429634692791997E-4</v>
+      </c>
+      <c r="AF14" s="1">
+        <v>1.6050076237862E-4</v>
+      </c>
+      <c r="AG14">
+        <v>2.1973136344593499E-3</v>
+      </c>
+      <c r="AH14" s="1">
+        <v>1.8536691745719999E-4</v>
       </c>
       <c r="AI14">
-        <v>3.6479497598817801E-3</v>
+        <v>3.2554488363501998E-3</v>
       </c>
       <c r="AJ14" s="1">
-        <v>3.7788018433178999E-4</v>
-      </c>
-      <c r="AK14">
-        <v>4.9117375643735299E-3</v>
+        <v>1.1059907834101001E-4</v>
+      </c>
+      <c r="AK14" s="1">
+        <v>3.4233322418360002E-4</v>
       </c>
     </row>
     <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B15">
-        <v>1.32577772190579E-2</v>
+        <v>1.40217191594704E-3</v>
       </c>
       <c r="C15" s="1">
-        <v>3.2747401335248E-4</v>
-      </c>
-      <c r="D15">
-        <v>0.27852352149905402</v>
+        <v>7.9227583875601999E-4</v>
+      </c>
+      <c r="D15" s="1">
+        <v>9.4067182781942802E-6</v>
       </c>
       <c r="E15">
-        <v>2.7617591884944001E-3</v>
-      </c>
-      <c r="F15">
-        <v>2.35992597284843E-3</v>
-      </c>
-      <c r="G15">
-        <v>5.4647216958265297E-3</v>
+        <v>1.12902105190022E-3</v>
+      </c>
+      <c r="F15" s="1">
+        <v>2.7325458632981002E-4</v>
+      </c>
+      <c r="G15" s="1">
+        <v>3.0849235379665002E-4</v>
       </c>
       <c r="H15" s="1">
-        <v>2.1027756638763E-4</v>
+        <v>3.0039652341090198E-5</v>
       </c>
       <c r="I15" s="1">
-        <v>6.4816892279310004E-4</v>
-      </c>
-      <c r="J15">
-        <v>1.6610882305366399E-2</v>
+        <v>1.24647869767905E-5</v>
+      </c>
+      <c r="J15" s="1">
+        <v>2.8617999477410002E-4</v>
       </c>
       <c r="K15" s="1">
-        <v>5.7099352874000002E-4</v>
-      </c>
-      <c r="L15">
-        <v>0.41970890442546399</v>
-      </c>
-      <c r="M15">
-        <v>3.8121615734113398E-3</v>
+        <v>7.0122012301404406E-5</v>
+      </c>
+      <c r="L15" s="1">
+        <v>9.2235606633584807E-6</v>
+      </c>
+      <c r="M15" s="1">
+        <v>1.0891890209745999E-4</v>
       </c>
       <c r="N15" s="1">
-        <v>9.0845355531198003E-4</v>
-      </c>
-      <c r="O15">
-        <v>3.8129680221702399E-3</v>
+        <v>2.9623485499303799E-5</v>
+      </c>
+      <c r="O15" s="1">
+        <v>9.8272371705418707E-5</v>
       </c>
       <c r="P15" s="1">
-        <v>2.1860790486183E-4</v>
-      </c>
-      <c r="Q15">
-        <v>1.0575060667453299E-3</v>
-      </c>
-      <c r="R15">
-        <v>7.6814580000000004E-3</v>
-      </c>
-      <c r="S15">
-        <v>1.1124321E-2</v>
-      </c>
-      <c r="T15">
-        <v>1.6415749999999999E-3</v>
+        <v>8.74431619447359E-6</v>
+      </c>
+      <c r="Q15" s="1">
+        <v>1.11316428078455E-5</v>
+      </c>
+      <c r="R15" s="1">
+        <v>5.6417499999999998E-4</v>
+      </c>
+      <c r="S15" s="1">
+        <v>1.4746400000000001E-4</v>
+      </c>
+      <c r="T15" s="1">
+        <v>1.18312E-4</v>
       </c>
       <c r="U15">
-        <v>0.26917912799999999</v>
-      </c>
-      <c r="V15">
-        <v>7.0896420000000002E-3</v>
-      </c>
-      <c r="W15">
-        <v>0.30447917600000002</v>
+        <v>2.5725909999999999E-3</v>
+      </c>
+      <c r="V15" s="1">
+        <v>1.2016299999999999E-4</v>
+      </c>
+      <c r="W15" s="1">
+        <v>4.9944599999999996E-4</v>
       </c>
       <c r="X15">
-        <v>1.7423436778275399E-2</v>
-      </c>
-      <c r="Y15" s="1">
-        <v>6.8735790197217998E-4</v>
-      </c>
-      <c r="Z15" s="1">
-        <v>7.5323119061883998E-4</v>
-      </c>
-      <c r="AA15">
-        <v>1.94898832860168E-3</v>
+        <v>1.7509372348081999E-3</v>
+      </c>
+      <c r="Y15">
+        <v>1.8770158092317401E-3</v>
+      </c>
+      <c r="Z15">
+        <v>1.88307797654711E-3</v>
+      </c>
+      <c r="AA15" s="1">
+        <v>4.9569645351718995E-4</v>
       </c>
       <c r="AB15">
-        <v>1.3617960986382001E-2</v>
+        <v>1.61534372060687E-3</v>
       </c>
       <c r="AC15" s="1">
-        <v>8.0346799207742996E-4</v>
-      </c>
-      <c r="AD15">
-        <v>7.7516604307273597E-3</v>
-      </c>
-      <c r="AE15">
-        <v>1.7420445052023999E-2</v>
-      </c>
-      <c r="AF15">
-        <v>2.56801219805794E-3</v>
+        <v>2.1488097462534999E-4</v>
+      </c>
+      <c r="AD15" s="1">
+        <v>9.4881755849549E-4</v>
+      </c>
+      <c r="AE15" s="1">
+        <v>2.9429634692791997E-4</v>
+      </c>
+      <c r="AF15" s="1">
+        <v>2.3071984591926001E-4</v>
       </c>
       <c r="AG15" s="1">
-        <v>4.8734193449098001E-4</v>
-      </c>
-      <c r="AH15">
-        <v>4.05626431141642E-3</v>
-      </c>
-      <c r="AI15">
-        <v>9.6739933505725802E-3</v>
-      </c>
-      <c r="AJ15">
-        <v>1.56682027649769E-3</v>
-      </c>
-      <c r="AK15">
-        <v>8.0225046884767597E-3</v>
+        <v>2.6504561349509001E-4</v>
+      </c>
+      <c r="AH15" s="1">
+        <v>1.6355904481516999E-4</v>
+      </c>
+      <c r="AI15" s="1">
+        <v>4.8485408200960001E-4</v>
+      </c>
+      <c r="AJ15" s="1">
+        <v>2.7649769585253399E-5</v>
+      </c>
+      <c r="AK15" s="1">
+        <v>1.1907242580299E-4</v>
       </c>
     </row>
     <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B16">
-        <v>4.9124367813868901E-3</v>
-      </c>
-      <c r="C16">
-        <v>3.5493957576269702E-3</v>
-      </c>
-      <c r="D16">
-        <v>0.31910410415118401</v>
+        <v>2.2144646120818802E-3</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1.05636778500802E-5</v>
+      </c>
+      <c r="D16" s="1">
+        <v>6.5847027947359997E-5</v>
       </c>
       <c r="E16">
-        <v>1.5146251650107599E-2</v>
+        <v>1.1463906065448399E-3</v>
       </c>
       <c r="F16">
-        <v>1.502900224814E-3</v>
+        <v>1.0495460247668001E-2</v>
       </c>
       <c r="G16">
-        <v>9.8056498171080995E-3</v>
-      </c>
-      <c r="H16" s="1">
-        <v>4.1054191532822998E-4</v>
-      </c>
-      <c r="I16" s="1">
-        <v>6.1077456186272997E-4</v>
+        <v>1.30007491957163E-3</v>
+      </c>
+      <c r="H16">
+        <v>1.0674089798534001E-2</v>
+      </c>
+      <c r="I16">
+        <v>1.93328846010021E-2</v>
       </c>
       <c r="J16" s="1">
-        <v>6.7190085729572E-4</v>
-      </c>
-      <c r="K16">
-        <v>1.04181275419229E-3</v>
-      </c>
-      <c r="L16">
-        <v>8.3593130292017898E-2</v>
-      </c>
-      <c r="M16">
-        <v>2.7696520819070099E-3</v>
+        <v>2.6129477783722E-4</v>
+      </c>
+      <c r="K16" s="1">
+        <v>4.0069721315088197E-5</v>
+      </c>
+      <c r="L16" s="1">
+        <v>4.6117803316792398E-5</v>
+      </c>
+      <c r="M16" s="1">
+        <v>1.4003858841102001E-4</v>
       </c>
       <c r="N16" s="1">
-        <v>2.2711338882798999E-4</v>
+        <v>7.7021062298190002E-4</v>
       </c>
       <c r="O16" s="1">
-        <v>8.8445134534875997E-4</v>
+        <v>2.7516264077516998E-4</v>
       </c>
       <c r="P16" s="1">
-        <v>1.5739769150052E-4</v>
-      </c>
-      <c r="Q16" s="1">
-        <v>1.5584299930983001E-4</v>
+        <v>6.7331234697446004E-4</v>
+      </c>
+      <c r="Q16">
+        <v>2.02595899102789E-3</v>
       </c>
       <c r="R16">
-        <v>6.2927199999999999E-3</v>
-      </c>
-      <c r="S16">
-        <v>1.188929E-3</v>
-      </c>
-      <c r="T16">
-        <v>0.638868349</v>
-      </c>
-      <c r="U16">
-        <v>0.13941189100000001</v>
-      </c>
-      <c r="V16">
-        <v>0.24700449799999999</v>
-      </c>
-      <c r="W16">
-        <v>1.8308950000000001E-2</v>
+        <v>1.0198550000000001E-3</v>
+      </c>
+      <c r="S16" s="1">
+        <v>9.2200000000000005E-5</v>
+      </c>
+      <c r="T16" s="1">
+        <v>2.0704499999999999E-4</v>
+      </c>
+      <c r="U16" s="1">
+        <v>7.1699999999999995E-5</v>
+      </c>
+      <c r="V16" s="1">
+        <v>1.7200000000000001E-5</v>
+      </c>
+      <c r="W16" s="1">
+        <v>2.44E-5</v>
       </c>
       <c r="X16">
-        <v>6.5633291439743001E-3</v>
+        <v>2.9970029970029901E-3</v>
       </c>
       <c r="Y16" s="1">
-        <v>6.1685965561606001E-4</v>
+        <v>6.3448421720509001E-4</v>
       </c>
       <c r="Z16" s="1">
-        <v>1.1127278952323E-4</v>
+        <v>1.7118890695881999E-4</v>
       </c>
       <c r="AA16">
-        <v>1.2505069622819999E-3</v>
+        <v>4.1458248839619603E-3</v>
       </c>
       <c r="AB16">
-        <v>3.1693452746084298E-3</v>
-      </c>
-      <c r="AC16" s="1">
-        <v>6.4464292387607001E-4</v>
+        <v>2.14697583118635E-3</v>
+      </c>
+      <c r="AC16">
+        <v>8.9128891214170902E-3</v>
       </c>
       <c r="AD16">
-        <v>1.79022180848207E-3</v>
+        <v>4.7082833563078397E-3</v>
       </c>
       <c r="AE16" s="1">
-        <v>5.9808612440190995E-4</v>
+        <v>2.5632262474367001E-4</v>
       </c>
       <c r="AF16" s="1">
-        <v>5.7178396597382997E-4</v>
+        <v>7.0219083540646799E-5</v>
       </c>
       <c r="AG16" s="1">
-        <v>5.9849009498892703E-5</v>
+        <v>6.8398867998734606E-5</v>
       </c>
       <c r="AH16" s="1">
-        <v>3.4892596227237998E-4</v>
+        <v>3.5982989859339001E-4</v>
       </c>
       <c r="AI16" s="1">
-        <v>4.1558921315108002E-4</v>
+        <v>3.2323605467305999E-4</v>
       </c>
       <c r="AJ16" s="1">
-        <v>2.3963133640552E-4</v>
+        <v>9.0322580645161004E-4</v>
       </c>
       <c r="AK16" s="1">
-        <v>1.7860863870449001E-4</v>
+        <v>2.8279701128211001E-4</v>
       </c>
     </row>
     <row r="17" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>52</v>
-      </c>
-      <c r="B17">
-        <v>4.9124367813868901E-3</v>
+        <v>46</v>
+      </c>
+      <c r="B17" s="1">
+        <v>5.4152846408988999E-4</v>
       </c>
       <c r="C17" s="1">
-        <v>1.584551677512E-4</v>
+        <v>4.8592918110369E-4</v>
       </c>
       <c r="D17" s="1">
-        <v>4.4211575907512999E-4</v>
+        <v>1.3169405589471999E-4</v>
       </c>
       <c r="E17">
-        <v>3.2654762731883502E-3</v>
+        <v>1.8411727923296E-3</v>
       </c>
       <c r="F17">
-        <v>6.6276657847995898E-2</v>
-      </c>
-      <c r="G17">
-        <v>3.21713454673659E-3</v>
+        <v>1.7388928220988401E-3</v>
+      </c>
+      <c r="G17" s="1">
+        <v>5.5087920320831996E-4</v>
       </c>
       <c r="H17" s="1">
-        <v>1.5019826170545E-4</v>
+        <v>2.0026434894060099E-5</v>
       </c>
       <c r="I17" s="1">
-        <v>1.9943659162864001E-4</v>
-      </c>
-      <c r="J17">
-        <v>1.65486692630243E-3</v>
+        <v>1.7450701767506E-4</v>
+      </c>
+      <c r="J17" s="1">
+        <v>1.9908173549501999E-4</v>
       </c>
       <c r="K17" s="1">
-        <v>1.1019173361649E-4</v>
+        <v>9.0156872958948504E-5</v>
       </c>
       <c r="L17" s="1">
-        <v>2.76706819900754E-5</v>
+        <v>9.2235606633584807E-6</v>
       </c>
       <c r="M17" s="1">
-        <v>7.7799215783904004E-4</v>
-      </c>
-      <c r="N17">
-        <v>1.9472504468209001E-2</v>
-      </c>
-      <c r="O17">
-        <v>2.5354271899998E-3</v>
+        <v>2.6451733366526998E-4</v>
+      </c>
+      <c r="N17" s="1">
+        <v>4.1472879699025E-4</v>
+      </c>
+      <c r="O17" s="1">
+        <v>1.3758132038758E-4</v>
       </c>
       <c r="P17" s="1">
-        <v>1.8363064008394001E-4</v>
+        <v>8.74431619447359E-6</v>
       </c>
       <c r="Q17" s="1">
-        <v>2.2263285615691098E-5</v>
-      </c>
-      <c r="R17">
-        <v>2.734078E-3</v>
-      </c>
-      <c r="S17">
-        <v>1.5207230000000001E-3</v>
+        <v>4.4526571231382298E-5</v>
+      </c>
+      <c r="R17" s="1">
+        <v>8.8966000000000002E-4</v>
+      </c>
+      <c r="S17" s="1">
+        <v>2.30413E-4</v>
       </c>
       <c r="T17" s="1">
-        <v>9.3170500000000001E-4</v>
-      </c>
-      <c r="U17" s="1">
-        <v>3.4847799999999999E-4</v>
+        <v>2.5141200000000001E-4</v>
+      </c>
+      <c r="U17">
+        <v>2.7673289999999998E-3</v>
       </c>
       <c r="V17" s="1">
-        <v>7.7247899999999996E-4</v>
+        <v>1.02997E-4</v>
       </c>
       <c r="W17" s="1">
-        <v>1.21816E-4</v>
-      </c>
-      <c r="X17">
-        <v>5.5428442525216701E-3</v>
-      </c>
-      <c r="Y17" s="1">
-        <v>4.3180175893124E-4</v>
+        <v>4.2635600000000002E-4</v>
+      </c>
+      <c r="X17" s="1">
+        <v>6.6600066600066004E-4</v>
+      </c>
+      <c r="Y17">
+        <v>1.4011526463279199E-3</v>
       </c>
       <c r="Z17">
-        <v>1.1555251219720899E-3</v>
+        <v>3.8175126251818801E-3</v>
       </c>
       <c r="AA17">
-        <v>4.6088504348609699E-2</v>
+        <v>1.56595015997476E-3</v>
       </c>
       <c r="AB17">
-        <v>3.6805299963194702E-3</v>
+        <v>1.11029321555637E-2</v>
       </c>
       <c r="AC17" s="1">
-        <v>6.5398557494674001E-4</v>
-      </c>
-      <c r="AD17">
-        <v>2.8643548935713102E-3</v>
-      </c>
-      <c r="AE17">
-        <v>2.2594364699627801E-3</v>
+        <v>3.73706042826712E-5</v>
+      </c>
+      <c r="AD17" s="1">
+        <v>3.5804436169640998E-4</v>
+      </c>
+      <c r="AE17" s="1">
+        <v>1.6138831928305E-4</v>
       </c>
       <c r="AF17" s="1">
-        <v>7.2225343070378997E-4</v>
-      </c>
-      <c r="AG17" s="1">
-        <v>3.4199433999367002E-4</v>
-      </c>
-      <c r="AH17">
-        <v>1.5832515538109201E-2</v>
-      </c>
-      <c r="AI17">
-        <v>2.7244181751015801E-3</v>
+        <v>2.0062595297327E-4</v>
+      </c>
+      <c r="AG17">
+        <v>1.0687323124802201E-3</v>
+      </c>
+      <c r="AH17" s="1">
+        <v>3.3802202595135998E-4</v>
+      </c>
+      <c r="AI17" s="1">
+        <v>8.7735500554117995E-4</v>
       </c>
       <c r="AJ17" s="1">
-        <v>1.4746543778801E-4</v>
+        <v>1.84331797235023E-5</v>
       </c>
       <c r="AK17" s="1">
-        <v>7.8885482094482999E-4</v>
+        <v>1.0418837257762E-4</v>
       </c>
     </row>
     <row r="18" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>53</v>
-      </c>
-      <c r="B18">
-        <v>1.4892032762472E-3</v>
+        <v>39</v>
+      </c>
+      <c r="B18" s="1">
+        <v>3.0944483662279001E-4</v>
       </c>
       <c r="C18" s="1">
-        <v>3.5916504690271998E-4</v>
+        <v>1.05636778500802E-5</v>
       </c>
       <c r="D18">
-        <v>1.44957528666973E-2</v>
-      </c>
-      <c r="E18">
-        <v>2.8486069617175E-3</v>
-      </c>
-      <c r="F18">
-        <v>2.43693408354137E-2</v>
-      </c>
-      <c r="G18">
-        <v>2.31369265347494E-3</v>
+        <v>2.4833736254432901E-3</v>
+      </c>
+      <c r="E18" s="1">
+        <v>1.5632599180157001E-4</v>
+      </c>
+      <c r="F18" s="1">
+        <v>4.9682652059966897E-5</v>
+      </c>
+      <c r="G18" s="1">
+        <v>8.8140672513331204E-5</v>
       </c>
       <c r="H18" s="1">
-        <v>1.2015860936435999E-4</v>
+        <v>1.0013217447030001E-5</v>
       </c>
       <c r="I18" s="1">
-        <v>7.6035200558421999E-4</v>
-      </c>
-      <c r="J18">
-        <v>6.4452711866515699E-3</v>
+        <v>4.9859147907162197E-5</v>
+      </c>
+      <c r="J18" s="1">
+        <v>1.8663912702658001E-4</v>
       </c>
       <c r="K18" s="1">
-        <v>8.9155129926071005E-4</v>
+        <v>8.0139442630176503E-5</v>
       </c>
       <c r="L18">
-        <v>5.6374402774446997E-2</v>
-      </c>
-      <c r="M18">
-        <v>4.9635899670131302E-3</v>
-      </c>
-      <c r="N18">
-        <v>5.5287298436867402E-2</v>
-      </c>
-      <c r="O18">
-        <v>7.2525010318598999E-3</v>
+        <v>3.5879650980464401E-3</v>
+      </c>
+      <c r="M18" s="1">
+        <v>6.2239372627123898E-5</v>
+      </c>
+      <c r="N18" s="1">
+        <v>5.9246970998607699E-5</v>
+      </c>
+      <c r="O18" s="1">
+        <v>7.8617897364334895E-5</v>
       </c>
       <c r="P18" s="1">
-        <v>4.4596012591815E-4</v>
+        <v>8.74431619447359E-6</v>
       </c>
       <c r="Q18" s="1">
-        <v>8.5713649620410004E-4</v>
-      </c>
-      <c r="R18">
-        <v>1.3127919999999999E-3</v>
-      </c>
-      <c r="S18">
-        <v>3.9262309999999996E-3</v>
+        <v>1.11316428078455E-5</v>
+      </c>
+      <c r="R18" s="1">
+        <v>9.7600000000000001E-5</v>
+      </c>
+      <c r="S18" s="1">
+        <v>1.65897E-4</v>
       </c>
       <c r="T18" s="1">
-        <v>5.6198100000000003E-4</v>
-      </c>
-      <c r="U18" s="1">
-        <v>1.02494E-4</v>
-      </c>
-      <c r="V18">
-        <v>2.1114430000000002E-3</v>
-      </c>
-      <c r="W18" s="1">
-        <v>1.7054200000000001E-4</v>
-      </c>
-      <c r="X18">
-        <v>1.0097429452268099E-3</v>
+        <v>2.9600000000000001E-5</v>
+      </c>
+      <c r="U18">
+        <v>4.3867289999999998E-3</v>
+      </c>
+      <c r="V18" s="1">
+        <v>1.5449600000000001E-4</v>
+      </c>
+      <c r="W18">
+        <v>2.4241390000000001E-3</v>
+      </c>
+      <c r="X18" s="1">
+        <v>2.0409697829052001E-4</v>
       </c>
       <c r="Y18" s="1">
-        <v>2.5555614304093998E-4</v>
+        <v>8.8122807945152297E-6</v>
       </c>
       <c r="Z18" s="1">
-        <v>3.6805614996147999E-4</v>
-      </c>
-      <c r="AA18">
-        <v>1.08827903204001E-2</v>
-      </c>
-      <c r="AB18">
-        <v>2.4741340530814201E-3</v>
+        <v>3.4237781391765797E-5</v>
+      </c>
+      <c r="AA18" s="1">
+        <v>5.6329142445135401E-5</v>
+      </c>
+      <c r="AB18" s="1">
+        <v>4.7028994397415002E-4</v>
       </c>
       <c r="AC18" s="1">
-        <v>3.0830748533203E-4</v>
+        <v>3.73706042826712E-5</v>
       </c>
       <c r="AD18" s="1">
-        <v>9.3091534041066996E-4</v>
-      </c>
-      <c r="AE18">
-        <v>1.73729778992936E-3</v>
+        <v>1.6111996276337999E-4</v>
+      </c>
+      <c r="AE18" s="1">
+        <v>2.4682919419760998E-4</v>
       </c>
       <c r="AF18" s="1">
-        <v>5.7178396597382997E-4</v>
+        <v>2.0062595297327599E-5</v>
       </c>
       <c r="AG18" s="1">
-        <v>7.6948726498576002E-4</v>
-      </c>
-      <c r="AH18">
-        <v>2.3705157561879801E-2</v>
-      </c>
-      <c r="AI18">
-        <v>3.6479497598817801E-3</v>
+        <v>1.7099716999683601E-5</v>
+      </c>
+      <c r="AH18" s="1">
+        <v>3.2711808963035603E-5</v>
+      </c>
+      <c r="AI18" s="1">
+        <v>9.2353158478019893E-5</v>
       </c>
       <c r="AJ18" s="1">
-        <v>3.7788018433178999E-4</v>
-      </c>
-      <c r="AK18">
-        <v>1.7712023338195401E-3</v>
+        <v>1.84331797235023E-5</v>
+      </c>
+      <c r="AK18" s="1">
+        <v>1.3395647902835999E-4</v>
       </c>
     </row>
     <row r="19" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>54</v>
-      </c>
-      <c r="B19">
-        <v>5.1058398042761396E-3</v>
+        <v>43</v>
+      </c>
+      <c r="B19" s="1">
+        <v>3.8680604577849503E-5</v>
       </c>
       <c r="C19" s="1">
-        <v>8.9791261725682004E-4</v>
-      </c>
-      <c r="D19">
-        <v>1.72707347587647E-2</v>
-      </c>
-      <c r="E19">
-        <v>3.3175849371222099E-3</v>
-      </c>
-      <c r="F19">
-        <v>1.1302803343642401E-3</v>
-      </c>
-      <c r="G19">
-        <v>5.7511788814948598E-3</v>
+        <v>2.1127355700160501E-5</v>
+      </c>
+      <c r="D19" s="1">
+        <v>9.4067182781942802E-6</v>
+      </c>
+      <c r="E19" s="1">
+        <v>1.7369554644618901E-5</v>
+      </c>
+      <c r="F19" s="1">
+        <v>3.72619890449752E-5</v>
+      </c>
+      <c r="G19" s="1">
+        <v>8.8140672513331204E-5</v>
       </c>
       <c r="H19" s="1">
-        <v>5.2068730724555998E-4</v>
+        <v>6.0079304682180397E-5</v>
       </c>
       <c r="I19" s="1">
-        <v>4.1133797023407999E-4</v>
-      </c>
-      <c r="J19">
-        <v>1.03024798118677E-2</v>
-      </c>
-      <c r="K19">
-        <v>1.34233566405545E-3</v>
-      </c>
-      <c r="L19">
-        <v>3.3767455588555401E-2</v>
-      </c>
-      <c r="M19">
-        <v>8.2933964025642595E-3</v>
-      </c>
-      <c r="N19">
-        <v>1.65891518796101E-3</v>
-      </c>
-      <c r="O19">
-        <v>1.14978674895339E-2</v>
+        <v>1.9943659162864001E-4</v>
+      </c>
+      <c r="J19" s="1">
+        <v>1.4931130162126999E-4</v>
+      </c>
+      <c r="K19" s="1">
+        <v>1.0017430328772E-5</v>
+      </c>
+      <c r="L19" s="1">
+        <v>9.2235606633584807E-6</v>
+      </c>
+      <c r="M19" s="1">
+        <v>2.3339764735171001E-4</v>
+      </c>
+      <c r="N19" s="1">
+        <v>2.3698788399443001E-4</v>
+      </c>
+      <c r="O19" s="1">
+        <v>3.3412606379842002E-4</v>
       </c>
       <c r="P19" s="1">
-        <v>9.0066456803077999E-4</v>
-      </c>
-      <c r="Q19" s="1">
-        <v>4.4526571231381999E-4</v>
-      </c>
-      <c r="R19">
-        <v>8.8423570000000003E-3</v>
-      </c>
-      <c r="S19">
-        <v>1.5207233000000001E-2</v>
-      </c>
-      <c r="T19">
-        <v>3.0908929999999999E-3</v>
-      </c>
-      <c r="U19">
-        <v>0.29037481900000001</v>
-      </c>
-      <c r="V19">
-        <v>1.6685549000000001E-2</v>
-      </c>
-      <c r="W19">
-        <v>0.44331290899999998</v>
-      </c>
-      <c r="X19">
-        <v>6.7781680684906396E-3</v>
+        <v>7.5201119272471999E-4</v>
+      </c>
+      <c r="Q19">
+        <v>1.52503506467484E-3</v>
+      </c>
+      <c r="R19" s="1">
+        <v>4.3399999999999998E-5</v>
+      </c>
+      <c r="S19" s="1">
+        <v>1.75114E-4</v>
+      </c>
+      <c r="T19" s="1">
+        <v>2.9600000000000001E-5</v>
+      </c>
+      <c r="U19" s="1">
+        <v>1.0200000000000001E-5</v>
+      </c>
+      <c r="V19" s="1">
+        <v>2.7465900000000001E-4</v>
+      </c>
+      <c r="W19" s="1">
+        <v>6.0900000000000003E-5</v>
+      </c>
+      <c r="X19" s="1">
+        <v>4.29677849032687E-5</v>
       </c>
       <c r="Y19" s="1">
-        <v>8.6360351786248998E-4</v>
+        <v>8.8122807945152297E-6</v>
       </c>
       <c r="Z19" s="1">
-        <v>6.6763673713943E-4</v>
-      </c>
-      <c r="AA19">
-        <v>3.0305078635482802E-3</v>
-      </c>
-      <c r="AB19">
-        <v>6.56361182676972E-3</v>
-      </c>
-      <c r="AC19">
-        <v>1.81247430770955E-3</v>
-      </c>
-      <c r="AD19">
-        <v>3.7952702339819899E-3</v>
-      </c>
-      <c r="AE19">
-        <v>1.2388926862611E-2</v>
-      </c>
-      <c r="AF19">
-        <v>3.8720808923842298E-3</v>
-      </c>
-      <c r="AG19">
-        <v>1.9066184454647199E-3</v>
-      </c>
-      <c r="AH19">
-        <v>7.3274452077199802E-3</v>
-      </c>
-      <c r="AI19">
-        <v>1.50766531215367E-2</v>
-      </c>
-      <c r="AJ19">
-        <v>2.3410138248847901E-3</v>
-      </c>
-      <c r="AK19">
-        <v>8.42437412556187E-3</v>
+        <v>8.5594453479414492E-6</v>
+      </c>
+      <c r="AA19" s="1">
+        <v>4.5063313956108302E-5</v>
+      </c>
+      <c r="AB19" s="1">
+        <v>1.0223694434219999E-4</v>
+      </c>
+      <c r="AC19" s="1">
+        <v>2.8962218319069998E-4</v>
+      </c>
+      <c r="AD19" s="1">
+        <v>1.4321774467856001E-4</v>
+      </c>
+      <c r="AE19" s="1">
+        <v>6.6454013822434799E-5</v>
+      </c>
+      <c r="AF19" s="1">
+        <v>1.9059465532460999E-4</v>
+      </c>
+      <c r="AG19" s="1">
+        <v>9.4048443498260094E-5</v>
+      </c>
+      <c r="AH19" s="1">
+        <v>2.1807872642023001E-4</v>
+      </c>
+      <c r="AI19" s="1">
+        <v>1.8470631695603E-4</v>
+      </c>
+      <c r="AJ19" s="1">
+        <v>9.6774193548386999E-4</v>
+      </c>
+      <c r="AK19" s="1">
+        <v>8.1862292739558E-4</v>
       </c>
     </row>
     <row r="20" spans="1:37" x14ac:dyDescent="0.2">
@@ -2840,49 +2844,49 @@
     </row>
     <row r="21" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B21" s="1">
-        <v>5.8020906866774299E-5</v>
+        <v>5.9954937095666003E-4</v>
       </c>
       <c r="C21" s="1">
-        <v>1.05636778500802E-5</v>
+        <v>3.1691033550240797E-5</v>
       </c>
       <c r="D21" s="1">
-        <v>9.4067182781942802E-6</v>
+        <v>1.0347390106013E-4</v>
       </c>
       <c r="E21" s="1">
-        <v>6.9478218578475606E-5</v>
+        <v>2.0843465573542E-4</v>
       </c>
       <c r="F21" s="1">
-        <v>3.72619890449752E-5</v>
+        <v>8.6944641104942096E-5</v>
       </c>
       <c r="G21" s="1">
-        <v>1.7628134502665999E-4</v>
+        <v>3.5256269005331999E-4</v>
       </c>
       <c r="H21" s="1">
-        <v>1.0013217447030001E-5</v>
+        <v>4.0052869788120301E-5</v>
       </c>
       <c r="I21" s="1">
         <v>1.24647869767905E-5</v>
       </c>
       <c r="J21" s="1">
-        <v>2.48852169368786E-5</v>
+        <v>1.2442608468439E-4</v>
       </c>
       <c r="K21" s="1">
-        <v>1.0017430328772E-5</v>
+        <v>4.0069721315088197E-5</v>
       </c>
       <c r="L21" s="1">
         <v>9.2235606633584807E-6</v>
       </c>
       <c r="M21" s="1">
-        <v>1.7115827472459E-4</v>
+        <v>9.3359058940685799E-5</v>
       </c>
       <c r="N21" s="1">
         <v>9.8744951664346098E-6</v>
       </c>
       <c r="O21" s="1">
-        <v>1.96544743410837E-5</v>
+        <v>1.179268460465E-4</v>
       </c>
       <c r="P21" s="1">
         <v>8.74431619447359E-6</v>
@@ -2891,519 +2895,524 @@
         <v>1.11316428078455E-5</v>
       </c>
       <c r="R21" s="1">
-        <v>3.6888399999999999E-4</v>
+        <v>3.1463599999999997E-4</v>
       </c>
       <c r="S21" s="1">
-        <v>7.3731999999999997E-4</v>
+        <v>6.4499999999999996E-5</v>
       </c>
       <c r="T21" s="1">
-        <v>8.8700000000000001E-5</v>
-      </c>
-      <c r="U21" s="1">
-        <v>2.05E-5</v>
+        <v>1.03523E-4</v>
+      </c>
+      <c r="U21">
+        <v>3.55653E-3</v>
       </c>
       <c r="V21" s="1">
-        <v>5.1499999999999998E-5</v>
+        <v>3.43E-5</v>
       </c>
       <c r="W21" s="1">
-        <v>1.22E-5</v>
+        <v>7.5525899999999999E-4</v>
       </c>
       <c r="X21" s="1">
-        <v>9.6677516032354701E-5</v>
+        <v>6.3377482732320997E-4</v>
       </c>
       <c r="Y21" s="1">
-        <v>8.8122807945152297E-6</v>
+        <v>2.6436842383545699E-5</v>
       </c>
       <c r="Z21" s="1">
         <v>8.5594453479414492E-6</v>
       </c>
       <c r="AA21" s="1">
-        <v>1.1265828489026999E-5</v>
+        <v>1.0139245640124E-4</v>
       </c>
       <c r="AB21" s="1">
-        <v>6.1342166605324504E-5</v>
+        <v>3.8850038850037999E-4</v>
       </c>
       <c r="AC21" s="1">
-        <v>9.3426510706678102E-6</v>
+        <v>8.4083859636010299E-5</v>
       </c>
       <c r="AD21" s="1">
-        <v>8.9511090424103498E-5</v>
+        <v>4.8335988829014998E-4</v>
       </c>
       <c r="AE21" s="1">
-        <v>9.4934305460621203E-5</v>
+        <v>1.8986861092123999E-4</v>
       </c>
       <c r="AF21" s="1">
         <v>1.0031297648663799E-5</v>
       </c>
       <c r="AG21" s="1">
-        <v>8.5498584998418207E-6</v>
+        <v>1.7099716999683601E-5</v>
       </c>
       <c r="AH21" s="1">
-        <v>2.1807872642023701E-5</v>
+        <v>8.7231490568094995E-5</v>
       </c>
       <c r="AI21" s="1">
-        <v>4.6176579239009899E-5</v>
+        <v>1.1544144809751999E-4</v>
       </c>
       <c r="AJ21" s="1">
-        <v>9.21658986175115E-6</v>
+        <v>2.7649769585253399E-5</v>
       </c>
       <c r="AK21" s="1">
-        <v>4.4652159676122997E-5</v>
+        <v>1.3395647902835999E-4</v>
       </c>
     </row>
     <row r="22" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B22" s="1">
-        <v>5.9954937095666003E-4</v>
+        <v>3.8680604577849E-4</v>
       </c>
       <c r="C22" s="1">
-        <v>3.1691033550240797E-5</v>
+        <v>1.1620045635088E-4</v>
       </c>
       <c r="D22" s="1">
-        <v>1.0347390106013E-4</v>
+        <v>1.8813436556388499E-5</v>
       </c>
       <c r="E22" s="1">
-        <v>2.0843465573542E-4</v>
-      </c>
-      <c r="F22" s="1">
-        <v>8.6944641104942096E-5</v>
+        <v>5.0371708469394E-4</v>
+      </c>
+      <c r="F22">
+        <v>2.81949050440312E-3</v>
       </c>
       <c r="G22" s="1">
         <v>3.5256269005331999E-4</v>
       </c>
-      <c r="H22" s="1">
-        <v>4.0052869788120301E-5</v>
-      </c>
-      <c r="I22" s="1">
-        <v>1.24647869767905E-5</v>
+      <c r="H22">
+        <v>4.0353266311531199E-3</v>
+      </c>
+      <c r="I22">
+        <v>4.9859147907162201E-3</v>
       </c>
       <c r="J22" s="1">
         <v>1.2442608468439E-4</v>
       </c>
       <c r="K22" s="1">
-        <v>4.0069721315088197E-5</v>
+        <v>1.0017430328772E-5</v>
       </c>
       <c r="L22" s="1">
-        <v>9.2235606633584807E-6</v>
+        <v>2.213654559206E-4</v>
       </c>
       <c r="M22" s="1">
-        <v>9.3359058940685799E-5</v>
+        <v>3.1119686313561902E-5</v>
       </c>
       <c r="N22" s="1">
-        <v>9.8744951664346098E-6</v>
+        <v>3.3573283565876998E-4</v>
       </c>
       <c r="O22" s="1">
         <v>1.179268460465E-4</v>
       </c>
       <c r="P22" s="1">
-        <v>8.74431619447359E-6</v>
+        <v>6.3833508219657005E-4</v>
       </c>
       <c r="Q22" s="1">
-        <v>1.11316428078455E-5</v>
+        <v>9.6845292428255996E-4</v>
       </c>
       <c r="R22" s="1">
-        <v>3.1463599999999997E-4</v>
+        <v>3.5803400000000002E-4</v>
       </c>
       <c r="S22" s="1">
-        <v>6.4499999999999996E-5</v>
+        <v>4.6100000000000002E-5</v>
       </c>
       <c r="T22" s="1">
-        <v>1.03523E-4</v>
-      </c>
-      <c r="U22">
-        <v>3.55653E-3</v>
+        <v>8.8700000000000001E-5</v>
+      </c>
+      <c r="U22" s="1">
+        <v>2.05E-5</v>
       </c>
       <c r="V22" s="1">
-        <v>3.43E-5</v>
+        <v>1.3732999999999999E-4</v>
       </c>
       <c r="W22" s="1">
-        <v>7.5525899999999999E-4</v>
+        <v>2.44E-5</v>
       </c>
       <c r="X22" s="1">
-        <v>6.3377482732320997E-4</v>
+        <v>2.4706476319378998E-4</v>
       </c>
       <c r="Y22" s="1">
-        <v>2.6436842383545699E-5</v>
+        <v>4.4061403972576098E-5</v>
       </c>
       <c r="Z22" s="1">
-        <v>8.5594453479414492E-6</v>
+        <v>2.5678336043824298E-5</v>
       </c>
       <c r="AA22" s="1">
-        <v>1.0139245640124E-4</v>
+        <v>6.9848136631966995E-4</v>
       </c>
       <c r="AB22" s="1">
-        <v>3.8850038850037999E-4</v>
-      </c>
-      <c r="AC22" s="1">
-        <v>8.4083859636010299E-5</v>
+        <v>1.2268433321064001E-4</v>
+      </c>
+      <c r="AC22">
+        <v>2.2515789080309401E-3</v>
       </c>
       <c r="AD22" s="1">
-        <v>4.8335988829014998E-4</v>
+        <v>1.6111996276337999E-4</v>
       </c>
       <c r="AE22" s="1">
-        <v>1.8986861092123999E-4</v>
+        <v>6.6454013822434799E-5</v>
       </c>
       <c r="AF22" s="1">
         <v>1.0031297648663799E-5</v>
       </c>
       <c r="AG22" s="1">
-        <v>1.7099716999683601E-5</v>
+        <v>5.1299150999050901E-5</v>
       </c>
       <c r="AH22" s="1">
-        <v>8.7231490568094995E-5</v>
+        <v>1.1994329953113E-4</v>
       </c>
       <c r="AI22" s="1">
-        <v>1.1544144809751999E-4</v>
+        <v>1.3852973771701999E-4</v>
       </c>
       <c r="AJ22" s="1">
-        <v>2.7649769585253399E-5</v>
+        <v>3.5023041474653999E-4</v>
       </c>
       <c r="AK22" s="1">
-        <v>1.3395647902835999E-4</v>
+        <v>1.0418837257762E-4</v>
       </c>
     </row>
     <row r="23" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>58</v>
-      </c>
-      <c r="B23">
-        <v>1.35188712999584E-2</v>
+        <v>47</v>
+      </c>
+      <c r="B23" s="1">
+        <v>2.3208362746709001E-4</v>
       </c>
       <c r="C23" s="1">
-        <v>5.1762021465393004E-4</v>
+        <v>9.50731006507225E-5</v>
       </c>
       <c r="D23" s="1">
-        <v>6.3965684291721005E-4</v>
-      </c>
-      <c r="E23">
-        <v>4.3250191065100996E-3</v>
-      </c>
-      <c r="F23">
-        <v>1.3662729316490901E-3</v>
-      </c>
-      <c r="G23">
-        <v>5.4426865276981998E-3</v>
+        <v>9.4067182781942802E-6</v>
+      </c>
+      <c r="E23" s="1">
+        <v>1.7369554644618901E-5</v>
+      </c>
+      <c r="F23" s="1">
+        <v>3.72619890449752E-5</v>
+      </c>
+      <c r="G23" s="1">
+        <v>1.1017584064166E-4</v>
       </c>
       <c r="H23" s="1">
-        <v>2.9038330596386998E-4</v>
+        <v>3.0039652341090198E-5</v>
       </c>
       <c r="I23" s="1">
-        <v>3.8640839628049998E-4</v>
-      </c>
-      <c r="J23">
-        <v>1.9211387475270299E-2</v>
+        <v>2.4929573953581098E-5</v>
+      </c>
+      <c r="J23" s="1">
+        <v>1.2442608468439E-4</v>
       </c>
       <c r="K23" s="1">
-        <v>6.3109811071263998E-4</v>
-      </c>
-      <c r="L23">
-        <v>1.49421682746407E-3</v>
-      </c>
-      <c r="M23">
-        <v>5.5393041638140197E-3</v>
-      </c>
-      <c r="N23">
-        <v>1.09606896347424E-3</v>
-      </c>
-      <c r="O23">
-        <v>7.15422866015448E-3</v>
+        <v>1.1019173361649E-4</v>
+      </c>
+      <c r="L23" s="1">
+        <v>9.2235606633584807E-6</v>
+      </c>
+      <c r="M23" s="1">
+        <v>3.1119686313561902E-5</v>
+      </c>
+      <c r="N23" s="1">
+        <v>9.8744951664346098E-6</v>
+      </c>
+      <c r="O23" s="1">
+        <v>5.8963423023251198E-5</v>
       </c>
       <c r="P23" s="1">
-        <v>4.6344875830709999E-4</v>
+        <v>8.74431619447359E-6</v>
       </c>
       <c r="Q23" s="1">
-        <v>1.6697464211768001E-4</v>
-      </c>
-      <c r="R23">
-        <v>7.2040790000000004E-3</v>
-      </c>
-      <c r="S23">
-        <v>1.2774076000000001E-2</v>
-      </c>
-      <c r="T23">
-        <v>1.3310069999999999E-3</v>
+        <v>1.11316428078455E-5</v>
+      </c>
+      <c r="R23" s="1">
+        <v>9.7600000000000001E-5</v>
+      </c>
+      <c r="S23" s="1">
+        <v>9.2200000000000005E-5</v>
+      </c>
+      <c r="T23" s="1">
+        <v>1.4800000000000001E-5</v>
       </c>
       <c r="U23" s="1">
-        <v>4.9196999999999999E-4</v>
-      </c>
-      <c r="V23">
-        <v>4.5490440000000004E-3</v>
+        <v>7.7895199999999996E-4</v>
+      </c>
+      <c r="V23" s="1">
+        <v>8.5799999999999998E-5</v>
       </c>
       <c r="W23" s="1">
-        <v>8.4053100000000005E-4</v>
-      </c>
-      <c r="X23">
-        <v>1.12897854833338E-2</v>
+        <v>2.5581399999999999E-4</v>
+      </c>
+      <c r="X23" s="1">
+        <v>3.7596811790359999E-4</v>
       </c>
       <c r="Y23" s="1">
-        <v>6.9617018276669997E-4</v>
+        <v>8.7241579865699999E-4</v>
       </c>
       <c r="Z23" s="1">
-        <v>6.3339895574766002E-4</v>
-      </c>
-      <c r="AA23">
-        <v>2.1855707268712502E-3</v>
-      </c>
-      <c r="AB23">
-        <v>7.13613871508608E-3</v>
-      </c>
-      <c r="AC23">
-        <v>1.27060054561082E-3</v>
-      </c>
-      <c r="AD23">
-        <v>1.01505576540933E-2</v>
-      </c>
-      <c r="AE23">
-        <v>1.54647983595352E-2</v>
-      </c>
-      <c r="AF23">
-        <v>1.9460717438407799E-3</v>
-      </c>
-      <c r="AG23">
-        <v>1.03453287848086E-3</v>
-      </c>
-      <c r="AH23">
-        <v>4.9394831534183802E-3</v>
-      </c>
-      <c r="AI23">
-        <v>1.5169006280014699E-2</v>
-      </c>
-      <c r="AJ23">
-        <v>1.2626728110599001E-3</v>
-      </c>
-      <c r="AK23">
-        <v>1.4467299735063799E-2</v>
+        <v>8.5594453479414492E-6</v>
+      </c>
+      <c r="AA23" s="1">
+        <v>1.2392411337929001E-4</v>
+      </c>
+      <c r="AB23" s="1">
+        <v>1.6357911094753001E-4</v>
+      </c>
+      <c r="AC23" s="1">
+        <v>3.73706042826712E-5</v>
+      </c>
+      <c r="AD23" s="1">
+        <v>1.790221808482E-4</v>
+      </c>
+      <c r="AE23" s="1">
+        <v>1.0442773600667999E-4</v>
+      </c>
+      <c r="AF23" s="1">
+        <v>3.0093892945991002E-4</v>
+      </c>
+      <c r="AG23" s="1">
+        <v>2.5649575499525399E-5</v>
+      </c>
+      <c r="AH23" s="1">
+        <v>1.0903936321011E-4</v>
+      </c>
+      <c r="AI23" s="1">
+        <v>1.6161802733653E-4</v>
+      </c>
+      <c r="AJ23" s="1">
+        <v>9.21658986175115E-6</v>
+      </c>
+      <c r="AK23" s="1">
+        <v>5.9536212901497302E-5</v>
       </c>
     </row>
     <row r="24" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>59</v>
-      </c>
-      <c r="B24">
-        <v>1.15074798619102E-3</v>
-      </c>
-      <c r="C24" s="1">
-        <v>8.2396687230625997E-4</v>
+        <v>38</v>
+      </c>
+      <c r="B24" s="1">
+        <v>2.9010453433387002E-4</v>
+      </c>
+      <c r="C24">
+        <v>1.18313191920899E-3</v>
       </c>
       <c r="D24" s="1">
-        <v>3.7626873112777101E-5</v>
-      </c>
-      <c r="E24">
-        <v>1.5632599180156999E-3</v>
-      </c>
-      <c r="F24">
-        <v>7.5269217870849899E-3</v>
+        <v>9.4067182781942802E-6</v>
+      </c>
+      <c r="E24" s="1">
+        <v>7.8162995900784996E-4</v>
+      </c>
+      <c r="F24" s="1">
+        <v>9.9365304119933902E-5</v>
       </c>
       <c r="G24" s="1">
-        <v>7.9326605261998003E-4</v>
+        <v>6.6105504384998399E-5</v>
       </c>
       <c r="H24" s="1">
-        <v>7.0092522129210506E-5</v>
+        <v>4.0052869788120301E-5</v>
       </c>
       <c r="I24" s="1">
-        <v>6.2323934883952797E-5</v>
-      </c>
-      <c r="J24">
-        <v>1.4433425823389601E-3</v>
+        <v>3.7394360930371699E-5</v>
+      </c>
+      <c r="J24" s="1">
+        <v>6.2213042342196598E-5</v>
       </c>
       <c r="K24" s="1">
-        <v>5.8101095906877001E-4</v>
+        <v>3.5061006150702002E-4</v>
       </c>
       <c r="L24" s="1">
-        <v>3.1360106255417998E-4</v>
+        <v>2.76706819900754E-5</v>
       </c>
       <c r="M24" s="1">
-        <v>9.4915043256363005E-4</v>
-      </c>
-      <c r="N24">
-        <v>4.8187536412200903E-3</v>
+        <v>1.2447874525423999E-4</v>
+      </c>
+      <c r="N24" s="1">
+        <v>1.9748990332869199E-5</v>
       </c>
       <c r="O24" s="1">
-        <v>5.3067080720925995E-4</v>
+        <v>3.93089486821674E-5</v>
       </c>
       <c r="P24" s="1">
-        <v>1.1367611052815E-4</v>
+        <v>8.74431619447359E-6</v>
       </c>
       <c r="Q24" s="1">
-        <v>4.4526571231382298E-5</v>
+        <v>1.11316428078455E-5</v>
       </c>
       <c r="R24" s="1">
-        <v>4.0143200000000001E-4</v>
+        <v>1.19345E-4</v>
       </c>
       <c r="S24" s="1">
-        <v>5.6220700000000001E-4</v>
+        <v>2.76E-5</v>
       </c>
       <c r="T24" s="1">
-        <v>3.2535700000000002E-4</v>
-      </c>
-      <c r="U24" s="1">
-        <v>2.5623399999999999E-4</v>
+        <v>1.4800000000000001E-5</v>
+      </c>
+      <c r="U24">
+        <v>2.6648349999999999E-3</v>
       </c>
       <c r="V24" s="1">
-        <v>7.2098099999999999E-4</v>
+        <v>8.5799999999999998E-5</v>
       </c>
       <c r="W24" s="1">
         <v>3.6544799999999999E-4</v>
       </c>
       <c r="X24">
-        <v>1.53609831029185E-3</v>
-      </c>
-      <c r="Y24">
-        <v>1.63908422777983E-3</v>
+        <v>1.8261308583889001E-4</v>
+      </c>
+      <c r="Y24" s="1">
+        <v>7.8429299071185003E-4</v>
       </c>
       <c r="Z24">
-        <v>7.8746897201061299E-3</v>
-      </c>
-      <c r="AA24">
-        <v>9.7674732999864806E-3</v>
-      </c>
-      <c r="AB24">
-        <v>1.1246063877642801E-3</v>
+        <v>2.4822391509030199E-3</v>
+      </c>
+      <c r="AA24" s="1">
+        <v>2.0278491280247999E-4</v>
+      </c>
+      <c r="AB24" s="1">
+        <v>2.4536866642128999E-4</v>
       </c>
       <c r="AC24" s="1">
-        <v>1.4013976606001E-4</v>
-      </c>
-      <c r="AD24">
-        <v>1.25315526593744E-3</v>
-      </c>
-      <c r="AE24">
-        <v>1.6803372066529899E-3</v>
-      </c>
-      <c r="AF24">
-        <v>1.25391220608297E-3</v>
-      </c>
-      <c r="AG24">
-        <v>4.8221201939107903E-3</v>
-      </c>
-      <c r="AH24">
-        <v>9.5409442808853905E-3</v>
-      </c>
-      <c r="AI24">
-        <v>1.6392685629848501E-3</v>
+        <v>9.3426510706678102E-5</v>
+      </c>
+      <c r="AD24" s="1">
+        <v>1.6111996276337999E-4</v>
+      </c>
+      <c r="AE24" s="1">
+        <v>9.4934305460621206E-6</v>
+      </c>
+      <c r="AF24" s="1">
+        <v>2.7084503651392001E-4</v>
+      </c>
+      <c r="AG24" s="1">
+        <v>2.9924504749445998E-4</v>
+      </c>
+      <c r="AH24" s="1">
+        <v>2.1807872642023701E-5</v>
+      </c>
+      <c r="AI24" s="1">
+        <v>6.92648688585149E-5</v>
       </c>
       <c r="AJ24" s="1">
-        <v>1.0138248847926E-4</v>
-      </c>
-      <c r="AK24">
-        <v>2.1433036644538999E-3</v>
+        <v>2.7649769585253399E-5</v>
+      </c>
+      <c r="AK24" s="1">
+        <v>7.4420266126871593E-5</v>
       </c>
     </row>
     <row r="25" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>60</v>
-      </c>
-      <c r="B25">
-        <v>1.4118420670915001E-3</v>
+        <v>56</v>
+      </c>
+      <c r="B25" s="1">
+        <v>5.8020906866774299E-5</v>
       </c>
       <c r="C25" s="1">
-        <v>2.1127355700160501E-5</v>
+        <v>1.05636778500802E-5</v>
       </c>
       <c r="D25" s="1">
-        <v>2.5398139351124E-4</v>
-      </c>
-      <c r="E25">
-        <v>1.9801292294865502E-3</v>
-      </c>
-      <c r="F25">
-        <v>6.7444200171405096E-3</v>
-      </c>
-      <c r="G25">
-        <v>1.30007491957163E-3</v>
-      </c>
-      <c r="H25">
-        <v>1.99162895021428E-2</v>
-      </c>
-      <c r="I25">
-        <v>2.1090419564729599E-2</v>
-      </c>
-      <c r="J25">
-        <v>3.9567494929637001E-3</v>
+        <v>9.4067182781942802E-6</v>
+      </c>
+      <c r="E25" s="1">
+        <v>6.9478218578475606E-5</v>
+      </c>
+      <c r="F25" s="1">
+        <v>3.72619890449752E-5</v>
+      </c>
+      <c r="G25" s="1">
+        <v>1.7628134502665999E-4</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1.0013217447030001E-5</v>
+      </c>
+      <c r="I25" s="1">
+        <v>1.24647869767905E-5</v>
+      </c>
+      <c r="J25" s="1">
+        <v>2.48852169368786E-5</v>
       </c>
       <c r="K25" s="1">
-        <v>7.8135956564421996E-4</v>
-      </c>
-      <c r="L25">
-        <v>3.7447656293235401E-3</v>
-      </c>
-      <c r="M25">
-        <v>3.1275284745129698E-3</v>
-      </c>
-      <c r="N25">
-        <v>2.0588322422016098E-2</v>
-      </c>
-      <c r="O25">
-        <v>5.6801430845732004E-3</v>
-      </c>
-      <c r="P25">
-        <v>6.0475690800979302E-2</v>
-      </c>
-      <c r="Q25">
-        <v>0.12070040296546899</v>
+        <v>1.0017430328772E-5</v>
+      </c>
+      <c r="L25" s="1">
+        <v>9.2235606633584807E-6</v>
+      </c>
+      <c r="M25" s="1">
+        <v>1.7115827472459E-4</v>
+      </c>
+      <c r="N25" s="1">
+        <v>9.8744951664346098E-6</v>
+      </c>
+      <c r="O25" s="1">
+        <v>1.96544743410837E-5</v>
+      </c>
+      <c r="P25" s="1">
+        <v>8.74431619447359E-6</v>
+      </c>
+      <c r="Q25" s="1">
+        <v>1.11316428078455E-5</v>
       </c>
       <c r="R25" s="1">
-        <v>8.3541300000000002E-4</v>
-      </c>
-      <c r="S25">
-        <v>3.262643E-3</v>
+        <v>3.6888399999999999E-4</v>
+      </c>
+      <c r="S25" s="1">
+        <v>7.3731999999999997E-4</v>
       </c>
       <c r="T25" s="1">
-        <v>2.9577899999999997E-4</v>
+        <v>8.8700000000000001E-5</v>
       </c>
       <c r="U25" s="1">
-        <v>4.1E-5</v>
-      </c>
-      <c r="V25">
-        <v>1.459127E-3</v>
+        <v>2.05E-5</v>
+      </c>
+      <c r="V25" s="1">
+        <v>5.1499999999999998E-5</v>
       </c>
       <c r="W25" s="1">
-        <v>2.6799499999999998E-4</v>
+        <v>1.22E-5</v>
       </c>
       <c r="X25" s="1">
-        <v>5.2635536506503999E-4</v>
+        <v>9.6677516032354701E-5</v>
       </c>
       <c r="Y25" s="1">
-        <v>2.0268245827385E-4</v>
+        <v>8.8122807945152297E-6</v>
       </c>
       <c r="Z25" s="1">
-        <v>9.4153898827356E-5</v>
-      </c>
-      <c r="AA25">
-        <v>1.0927853634356199E-3</v>
+        <v>8.5594453479414492E-6</v>
+      </c>
+      <c r="AA25" s="1">
+        <v>1.1265828489026999E-5</v>
       </c>
       <c r="AB25" s="1">
-        <v>6.9521122152701E-4</v>
-      </c>
-      <c r="AC25">
-        <v>1.2986284988228201E-3</v>
+        <v>6.1342166605324504E-5</v>
+      </c>
+      <c r="AC25" s="1">
+        <v>9.3426510706678102E-6</v>
       </c>
       <c r="AD25" s="1">
-        <v>5.5496876062944005E-4</v>
-      </c>
-      <c r="AE25">
-        <v>1.5948963317384301E-3</v>
+        <v>8.9511090424103498E-5</v>
+      </c>
+      <c r="AE25" s="1">
+        <v>9.4934305460621203E-5</v>
       </c>
       <c r="AF25" s="1">
-        <v>1.3040686943262001E-4</v>
+        <v>1.0031297648663799E-5</v>
       </c>
       <c r="AG25" s="1">
-        <v>2.6504561349509001E-4</v>
-      </c>
-      <c r="AH25">
-        <v>1.8754770472140399E-3</v>
-      </c>
-      <c r="AI25">
-        <v>1.59309198374584E-3</v>
-      </c>
-      <c r="AJ25">
-        <v>2.8571428571428502E-3</v>
-      </c>
-      <c r="AK25">
-        <v>1.05676777900157E-3</v>
+        <v>8.5498584998418207E-6</v>
+      </c>
+      <c r="AH25" s="1">
+        <v>2.1807872642023701E-5</v>
+      </c>
+      <c r="AI25" s="1">
+        <v>4.6176579239009899E-5</v>
+      </c>
+      <c r="AJ25" s="1">
+        <v>9.21658986175115E-6</v>
+      </c>
+      <c r="AK25" s="1">
+        <v>4.4652159676122997E-5</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AK25" xr:uid="{2E11F963-3E5D-D04D-9A6E-5FE1391A4C26}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AK25">
+      <sortCondition descending="1" ref="J1:J25"/>
+    </sortState>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>